--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_office_equipment_services.xlsx
@@ -587,23 +587,26 @@
           <t>Office Equipment &amp; Services</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.265</v>
+      </c>
       <c r="G2">
-        <v>0.07561983471074381</v>
+        <v>-0.02609375</v>
       </c>
       <c r="H2">
-        <v>0.07561983471074381</v>
+        <v>-0.02609375</v>
       </c>
       <c r="I2">
-        <v>-0.02834710743801653</v>
+        <v>-0.00928125</v>
       </c>
       <c r="J2">
-        <v>-0.02834710743801653</v>
+        <v>-0.004640625</v>
       </c>
       <c r="K2">
-        <v>-1.43</v>
+        <v>-0.423</v>
       </c>
       <c r="L2">
-        <v>-0.05909090909090909</v>
+        <v>-0.01321875</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.9</v>
+        <v>7.7</v>
       </c>
       <c r="V2">
-        <v>0.02593085106382979</v>
+        <v>0.05</v>
       </c>
       <c r="W2">
-        <v>-0.146516393442623</v>
+        <v>-0.00896186440677966</v>
       </c>
       <c r="X2">
-        <v>0.1001136449695107</v>
+        <v>0.08443908509376256</v>
       </c>
       <c r="Y2">
-        <v>-0.2466300384121336</v>
+        <v>-0.09340094950054223</v>
       </c>
       <c r="Z2">
-        <v>1.446503287507471</v>
+        <v>0.6628003314001656</v>
       </c>
       <c r="AA2">
-        <v>-0.04100418410041841</v>
+        <v>-0.003075807787903893</v>
       </c>
       <c r="AB2">
-        <v>0.09863384676172238</v>
+        <v>0.08203851440540201</v>
       </c>
       <c r="AC2">
-        <v>-0.1396380308621408</v>
+        <v>-0.08511432219330591</v>
       </c>
       <c r="AD2">
-        <v>4.98</v>
+        <v>10.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.98</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
-        <v>1.080000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="AH2">
-        <v>0.03205045694426568</v>
+        <v>0.06382978723404255</v>
       </c>
       <c r="AI2">
-        <v>0.09543886546569566</v>
+        <v>0.1826086956521739</v>
       </c>
       <c r="AJ2">
-        <v>0.007129654079746504</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="AK2">
-        <v>0.0223695111847556</v>
+        <v>0.05622489959839357</v>
       </c>
       <c r="AL2">
-        <v>0.298</v>
+        <v>0.26</v>
       </c>
       <c r="AM2">
-        <v>0.291</v>
+        <v>0.207</v>
       </c>
       <c r="AN2">
-        <v>-14.43478260869565</v>
+        <v>194.4444444444445</v>
       </c>
       <c r="AO2">
-        <v>-2.302013422818792</v>
+        <v>-1.142307692307692</v>
       </c>
       <c r="AP2">
-        <v>-3.130434782608698</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AQ2">
-        <v>-2.357388316151203</v>
+        <v>-1.434782608695652</v>
       </c>
     </row>
     <row r="3">
@@ -712,23 +715,26 @@
           <t>Office Equipment &amp; Services</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.265</v>
+      </c>
       <c r="G3">
-        <v>0.07561983471074381</v>
+        <v>-0.02609375</v>
       </c>
       <c r="H3">
-        <v>0.07561983471074381</v>
+        <v>-0.02609375</v>
       </c>
       <c r="I3">
-        <v>-0.02834710743801653</v>
+        <v>-0.00928125</v>
       </c>
       <c r="J3">
-        <v>-0.02834710743801653</v>
+        <v>-0.004640625</v>
       </c>
       <c r="K3">
-        <v>-1.43</v>
+        <v>-0.423</v>
       </c>
       <c r="L3">
-        <v>-0.05909090909090909</v>
+        <v>-0.01321875</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.9</v>
+        <v>7.7</v>
       </c>
       <c r="V3">
-        <v>0.02593085106382979</v>
+        <v>0.05</v>
       </c>
       <c r="W3">
-        <v>-0.146516393442623</v>
+        <v>-0.00896186440677966</v>
       </c>
       <c r="X3">
-        <v>0.1001136449695107</v>
+        <v>0.08443908509376256</v>
       </c>
       <c r="Y3">
-        <v>-0.2466300384121336</v>
+        <v>-0.09340094950054223</v>
       </c>
       <c r="Z3">
-        <v>1.446503287507471</v>
+        <v>0.6628003314001656</v>
       </c>
       <c r="AA3">
-        <v>-0.04100418410041841</v>
+        <v>-0.003075807787903893</v>
       </c>
       <c r="AB3">
-        <v>0.09863384676172238</v>
+        <v>0.08203851440540201</v>
       </c>
       <c r="AC3">
-        <v>-0.1396380308621408</v>
+        <v>-0.08511432219330591</v>
       </c>
       <c r="AD3">
-        <v>4.98</v>
+        <v>10.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.98</v>
+        <v>10.5</v>
       </c>
       <c r="AG3">
-        <v>1.080000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="AH3">
-        <v>0.03205045694426568</v>
+        <v>0.06382978723404255</v>
       </c>
       <c r="AI3">
-        <v>0.09543886546569566</v>
+        <v>0.1826086956521739</v>
       </c>
       <c r="AJ3">
-        <v>0.007129654079746504</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="AK3">
-        <v>0.0223695111847556</v>
+        <v>0.05622489959839357</v>
       </c>
       <c r="AL3">
-        <v>0.298</v>
+        <v>0.26</v>
       </c>
       <c r="AM3">
-        <v>0.291</v>
+        <v>0.207</v>
       </c>
       <c r="AN3">
-        <v>-14.43478260869565</v>
+        <v>194.4444444444445</v>
       </c>
       <c r="AO3">
-        <v>-2.302013422818792</v>
+        <v>-1.142307692307692</v>
       </c>
       <c r="AP3">
-        <v>-3.130434782608698</v>
+        <v>51.85185185185185</v>
       </c>
       <c r="AQ3">
-        <v>-2.357388316151203</v>
+        <v>-1.434782608695652</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_office_equipment_services.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_office_equipment_services.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08522807086267077</v>
+        <v>0.08509361472094543</v>
       </c>
       <c r="C2">
-        <v>89.06916708939255</v>
+        <v>88.30442685845425</v>
       </c>
       <c r="D2">
-        <v>87.17916708939255</v>
+        <v>87.31842685845425</v>
       </c>
       <c r="E2">
-        <v>-42.5</v>
+        <v>-41.596</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.904</v>
       </c>
       <c r="G2">
         <v>1.89</v>
@@ -1570,28 +1570,28 @@
         <v>12.35</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0454712</v>
       </c>
       <c r="N2">
-        <v>12.35</v>
+        <v>12.3045288</v>
       </c>
       <c r="O2">
-        <v>2.47</v>
+        <v>2.46090576</v>
       </c>
       <c r="P2">
-        <v>9.879999999999999</v>
+        <v>9.843623040000001</v>
       </c>
       <c r="Q2">
-        <v>10.28</v>
+        <v>10.24362304</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08522807086267077</v>
+        <v>0.08554668153630851</v>
       </c>
       <c r="T2">
-        <v>0.7685264885431576</v>
+        <v>0.7747368036020923</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>271.6004855820827</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08509361472094543</v>
+        <v>0.08495915857922007</v>
       </c>
       <c r="C3">
-        <v>88.30442685845425</v>
+        <v>87.54013224571287</v>
       </c>
       <c r="D3">
-        <v>87.31842685845425</v>
+        <v>87.45813224571287</v>
       </c>
       <c r="E3">
-        <v>-41.596</v>
+        <v>-40.692</v>
       </c>
       <c r="F3">
-        <v>0.904</v>
+        <v>1.808</v>
       </c>
       <c r="G3">
         <v>1.89</v>
@@ -1652,28 +1652,28 @@
         <v>12.35</v>
       </c>
       <c r="M3">
-        <v>0.0454712</v>
+        <v>0.09094239999999999</v>
       </c>
       <c r="N3">
-        <v>12.3045288</v>
+        <v>12.2590576</v>
       </c>
       <c r="O3">
-        <v>2.46090576</v>
+        <v>2.45181152</v>
       </c>
       <c r="P3">
-        <v>9.843623040000001</v>
+        <v>9.807246080000001</v>
       </c>
       <c r="Q3">
-        <v>10.24362304</v>
+        <v>10.20724608</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08554668153630851</v>
+        <v>0.08587179446859192</v>
       </c>
       <c r="T3">
-        <v>0.7747368036020923</v>
+        <v>0.7810738597846786</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>271.6004855820827</v>
+        <v>135.8002427910414</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08495915857922007</v>
+        <v>0.08482470243749475</v>
       </c>
       <c r="C4">
-        <v>87.54013224571287</v>
+        <v>86.77628539350061</v>
       </c>
       <c r="D4">
-        <v>87.45813224571287</v>
+        <v>87.59828539350062</v>
       </c>
       <c r="E4">
-        <v>-40.692</v>
+        <v>-39.788</v>
       </c>
       <c r="F4">
-        <v>1.808</v>
+        <v>2.712</v>
       </c>
       <c r="G4">
         <v>1.89</v>
@@ -1734,28 +1734,28 @@
         <v>12.35</v>
       </c>
       <c r="M4">
-        <v>0.09094239999999999</v>
+        <v>0.1364136</v>
       </c>
       <c r="N4">
-        <v>12.2590576</v>
+        <v>12.2135864</v>
       </c>
       <c r="O4">
-        <v>2.45181152</v>
+        <v>2.44271728</v>
       </c>
       <c r="P4">
-        <v>9.807246080000001</v>
+        <v>9.77086912</v>
       </c>
       <c r="Q4">
-        <v>10.20724608</v>
+        <v>10.17086912</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08587179446859192</v>
+        <v>0.08620361076030386</v>
       </c>
       <c r="T4">
-        <v>0.7810738597846786</v>
+        <v>0.7875415769194831</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>135.8002427910414</v>
+        <v>90.53349519402758</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08482470243749475</v>
+        <v>0.08469024629576941</v>
       </c>
       <c r="C5">
-        <v>86.77628539350061</v>
+        <v>86.01288845790437</v>
       </c>
       <c r="D5">
-        <v>87.59828539350062</v>
+        <v>87.73888845790437</v>
       </c>
       <c r="E5">
-        <v>-39.788</v>
+        <v>-38.884</v>
       </c>
       <c r="F5">
-        <v>2.712</v>
+        <v>3.616</v>
       </c>
       <c r="G5">
         <v>1.89</v>
@@ -1816,28 +1816,28 @@
         <v>12.35</v>
       </c>
       <c r="M5">
-        <v>0.1364136</v>
+        <v>0.1818848</v>
       </c>
       <c r="N5">
-        <v>12.2135864</v>
+        <v>12.1681152</v>
       </c>
       <c r="O5">
-        <v>2.44271728</v>
+        <v>2.43362304</v>
       </c>
       <c r="P5">
-        <v>9.77086912</v>
+        <v>9.734492159999999</v>
       </c>
       <c r="Q5">
-        <v>10.17086912</v>
+        <v>10.13449216</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08620361076030386</v>
+        <v>0.08654233989142647</v>
       </c>
       <c r="T5">
-        <v>0.7875415769194831</v>
+        <v>0.794144038161263</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>90.53349519402758</v>
+        <v>67.90012139552069</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08469024629576941</v>
+        <v>0.08455579015404406</v>
       </c>
       <c r="C6">
-        <v>86.01288845790437</v>
+        <v>85.24994360887602</v>
       </c>
       <c r="D6">
-        <v>87.73888845790437</v>
+        <v>87.87994360887602</v>
       </c>
       <c r="E6">
-        <v>-38.884</v>
+        <v>-37.98</v>
       </c>
       <c r="F6">
-        <v>3.616</v>
+        <v>4.52</v>
       </c>
       <c r="G6">
         <v>1.89</v>
@@ -1898,28 +1898,28 @@
         <v>12.35</v>
       </c>
       <c r="M6">
-        <v>0.1818848</v>
+        <v>0.227356</v>
       </c>
       <c r="N6">
-        <v>12.1681152</v>
+        <v>12.122644</v>
       </c>
       <c r="O6">
-        <v>2.43362304</v>
+        <v>2.4245288</v>
       </c>
       <c r="P6">
-        <v>9.734492159999999</v>
+        <v>9.6981152</v>
       </c>
       <c r="Q6">
-        <v>10.13449216</v>
+        <v>10.0981152</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08654233989142647</v>
+        <v>0.08688820016215165</v>
       </c>
       <c r="T6">
-        <v>0.794144038161263</v>
+        <v>0.80088549858708</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>67.90012139552069</v>
+        <v>54.32009711641654</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08455579015404406</v>
+        <v>0.08442133401231872</v>
       </c>
       <c r="C7">
-        <v>85.24994360887602</v>
+        <v>84.48745303034418</v>
       </c>
       <c r="D7">
-        <v>87.87994360887602</v>
+        <v>88.02145303034419</v>
       </c>
       <c r="E7">
-        <v>-37.98</v>
+        <v>-37.076</v>
       </c>
       <c r="F7">
-        <v>4.52</v>
+        <v>5.424</v>
       </c>
       <c r="G7">
         <v>1.89</v>
@@ -1980,28 +1980,28 @@
         <v>12.35</v>
       </c>
       <c r="M7">
-        <v>0.227356</v>
+        <v>0.2728272</v>
       </c>
       <c r="N7">
-        <v>12.122644</v>
+        <v>12.0771728</v>
       </c>
       <c r="O7">
-        <v>2.4245288</v>
+        <v>2.41543456</v>
       </c>
       <c r="P7">
-        <v>9.6981152</v>
+        <v>9.66173824</v>
       </c>
       <c r="Q7">
-        <v>10.0981152</v>
+        <v>10.06173824</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08688820016215165</v>
+        <v>0.0872414191620412</v>
       </c>
       <c r="T7">
-        <v>0.80088549858708</v>
+        <v>0.8077703943411062</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.32009711641654</v>
+        <v>45.26674759701379</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08442133401231872</v>
+        <v>0.08428687787059339</v>
       </c>
       <c r="C8">
-        <v>84.48745303034418</v>
+        <v>83.72541892032696</v>
       </c>
       <c r="D8">
-        <v>88.02145303034419</v>
+        <v>88.16341892032696</v>
       </c>
       <c r="E8">
-        <v>-37.076</v>
+        <v>-36.172</v>
       </c>
       <c r="F8">
-        <v>5.424</v>
+        <v>6.327999999999999</v>
       </c>
       <c r="G8">
         <v>1.89</v>
@@ -2062,28 +2062,28 @@
         <v>12.35</v>
       </c>
       <c r="M8">
-        <v>0.2728272</v>
+        <v>0.3182984</v>
       </c>
       <c r="N8">
-        <v>12.0771728</v>
+        <v>12.0317016</v>
       </c>
       <c r="O8">
-        <v>2.41543456</v>
+        <v>2.40634032</v>
       </c>
       <c r="P8">
-        <v>9.66173824</v>
+        <v>9.62536128</v>
       </c>
       <c r="Q8">
-        <v>10.06173824</v>
+        <v>10.02536128</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0872414191620412</v>
+        <v>0.08760223426945525</v>
       </c>
       <c r="T8">
-        <v>0.8077703943411062</v>
+        <v>0.8148033523694124</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.26674759701379</v>
+        <v>38.80006936886896</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08428687787059337</v>
+        <v>0.08415242172886805</v>
       </c>
       <c r="C9">
-        <v>83.72541892032697</v>
+        <v>82.96384349104569</v>
       </c>
       <c r="D9">
-        <v>88.16341892032698</v>
+        <v>88.30584349104569</v>
       </c>
       <c r="E9">
-        <v>-36.172</v>
+        <v>-35.268</v>
       </c>
       <c r="F9">
-        <v>6.328000000000001</v>
+        <v>7.232</v>
       </c>
       <c r="G9">
         <v>1.89</v>
@@ -2144,28 +2144,28 @@
         <v>12.35</v>
       </c>
       <c r="M9">
-        <v>0.3182984</v>
+        <v>0.3637696</v>
       </c>
       <c r="N9">
-        <v>12.0317016</v>
+        <v>11.9862304</v>
       </c>
       <c r="O9">
-        <v>2.40634032</v>
+        <v>2.39724608</v>
       </c>
       <c r="P9">
-        <v>9.62536128</v>
+        <v>9.58898432</v>
       </c>
       <c r="Q9">
-        <v>10.02536128</v>
+        <v>9.988984319999998</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08760223426945525</v>
+        <v>0.08797089318355222</v>
       </c>
       <c r="T9">
-        <v>0.8148033523694124</v>
+        <v>0.8219892007896382</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.80006936886895</v>
+        <v>33.95006069776034</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08415242172886805</v>
+        <v>0.0840179655871427</v>
       </c>
       <c r="C10">
-        <v>82.96384349104569</v>
+        <v>82.20272896903991</v>
       </c>
       <c r="D10">
-        <v>88.30584349104569</v>
+        <v>88.44872896903991</v>
       </c>
       <c r="E10">
-        <v>-35.268</v>
+        <v>-34.364</v>
       </c>
       <c r="F10">
-        <v>7.232</v>
+        <v>8.136000000000001</v>
       </c>
       <c r="G10">
         <v>1.89</v>
@@ -2226,28 +2226,28 @@
         <v>12.35</v>
       </c>
       <c r="M10">
-        <v>0.3637696</v>
+        <v>0.4092408</v>
       </c>
       <c r="N10">
-        <v>11.9862304</v>
+        <v>11.9407592</v>
       </c>
       <c r="O10">
-        <v>2.39724608</v>
+        <v>2.38815184</v>
       </c>
       <c r="P10">
-        <v>9.58898432</v>
+        <v>9.55260736</v>
       </c>
       <c r="Q10">
-        <v>9.988984319999998</v>
+        <v>9.952607359999998</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08797089318355222</v>
+        <v>0.0883476544913656</v>
       </c>
       <c r="T10">
-        <v>0.8219892007896382</v>
+        <v>0.8293329799443745</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.95006069776034</v>
+        <v>30.17783173134253</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0840179655871427</v>
+        <v>0.08388350944541735</v>
       </c>
       <c r="C11">
-        <v>82.20272896903991</v>
+        <v>81.44207759528325</v>
       </c>
       <c r="D11">
-        <v>88.44872896903991</v>
+        <v>88.59207759528326</v>
       </c>
       <c r="E11">
-        <v>-34.364</v>
+        <v>-33.46</v>
       </c>
       <c r="F11">
-        <v>8.136000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G11">
         <v>1.89</v>
@@ -2308,28 +2308,28 @@
         <v>12.35</v>
       </c>
       <c r="M11">
-        <v>0.4092408</v>
+        <v>0.4547119999999999</v>
       </c>
       <c r="N11">
-        <v>11.9407592</v>
+        <v>11.895288</v>
       </c>
       <c r="O11">
-        <v>2.38815184</v>
+        <v>2.3790576</v>
       </c>
       <c r="P11">
-        <v>9.55260736</v>
+        <v>9.5162304</v>
       </c>
       <c r="Q11">
-        <v>9.952607359999998</v>
+        <v>9.916230399999998</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0883476544913656</v>
+        <v>0.08873278827268594</v>
       </c>
       <c r="T11">
-        <v>0.8293329799443745</v>
+        <v>0.8368399541914382</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.17783173134253</v>
+        <v>27.16004855820827</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08388350944541736</v>
+        <v>0.08374905330369201</v>
       </c>
       <c r="C12">
-        <v>81.44207759528324</v>
+        <v>80.68189162530079</v>
       </c>
       <c r="D12">
-        <v>88.59207759528324</v>
+        <v>88.73589162530079</v>
       </c>
       <c r="E12">
-        <v>-33.46</v>
+        <v>-32.556</v>
       </c>
       <c r="F12">
-        <v>9.040000000000001</v>
+        <v>9.944000000000001</v>
       </c>
       <c r="G12">
         <v>1.89</v>
@@ -2390,28 +2390,28 @@
         <v>12.35</v>
       </c>
       <c r="M12">
-        <v>0.454712</v>
+        <v>0.5001832</v>
       </c>
       <c r="N12">
-        <v>11.895288</v>
+        <v>11.8498168</v>
       </c>
       <c r="O12">
-        <v>2.3790576</v>
+        <v>2.36996336</v>
       </c>
       <c r="P12">
-        <v>9.5162304</v>
+        <v>9.479853439999999</v>
       </c>
       <c r="Q12">
-        <v>9.916230399999998</v>
+        <v>9.879853439999998</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08873278827268596</v>
+        <v>0.08912657674572136</v>
       </c>
       <c r="T12">
-        <v>0.8368399541914384</v>
+        <v>0.8445156244889979</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.16004855820827</v>
+        <v>24.69095323473479</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08374905330369201</v>
+        <v>0.08361459716196668</v>
       </c>
       <c r="C13">
-        <v>80.68189162530079</v>
+        <v>79.92217332928716</v>
       </c>
       <c r="D13">
-        <v>88.73589162530079</v>
+        <v>88.88017332928716</v>
       </c>
       <c r="E13">
-        <v>-32.556</v>
+        <v>-31.652</v>
       </c>
       <c r="F13">
-        <v>9.944000000000001</v>
+        <v>10.848</v>
       </c>
       <c r="G13">
         <v>1.89</v>
@@ -2472,28 +2472,28 @@
         <v>12.35</v>
       </c>
       <c r="M13">
-        <v>0.5001832</v>
+        <v>0.5456544</v>
       </c>
       <c r="N13">
-        <v>11.8498168</v>
+        <v>11.8043456</v>
       </c>
       <c r="O13">
-        <v>2.36996336</v>
+        <v>2.36086912</v>
       </c>
       <c r="P13">
-        <v>9.479853439999999</v>
+        <v>9.443476479999999</v>
       </c>
       <c r="Q13">
-        <v>9.879853439999998</v>
+        <v>9.843476479999998</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08912657674572136</v>
+        <v>0.08952931495678032</v>
       </c>
       <c r="T13">
-        <v>0.8445156244889979</v>
+        <v>0.8523657418387749</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.69095323473479</v>
+        <v>22.6333737985069</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08361459716196668</v>
+        <v>0.08348014102024134</v>
       </c>
       <c r="C14">
-        <v>79.92217332928716</v>
+        <v>79.16292499222617</v>
       </c>
       <c r="D14">
-        <v>88.88017332928716</v>
+        <v>89.02492499222616</v>
       </c>
       <c r="E14">
-        <v>-31.652</v>
+        <v>-30.748</v>
       </c>
       <c r="F14">
-        <v>10.848</v>
+        <v>11.752</v>
       </c>
       <c r="G14">
         <v>1.89</v>
@@ -2554,28 +2554,28 @@
         <v>12.35</v>
       </c>
       <c r="M14">
-        <v>0.5456544</v>
+        <v>0.5911256</v>
       </c>
       <c r="N14">
-        <v>11.8043456</v>
+        <v>11.7588744</v>
       </c>
       <c r="O14">
-        <v>2.36086912</v>
+        <v>2.35177488</v>
       </c>
       <c r="P14">
-        <v>9.443476479999999</v>
+        <v>9.407099519999999</v>
       </c>
       <c r="Q14">
-        <v>9.843476479999998</v>
+        <v>9.807099519999998</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08952931495678032</v>
+        <v>0.08994131151751877</v>
       </c>
       <c r="T14">
-        <v>0.8523657418387749</v>
+        <v>0.8603963216563626</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.6333737985069</v>
+        <v>20.89234504477559</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08348014102024134</v>
+        <v>0.083345684878516</v>
       </c>
       <c r="C15">
-        <v>79.16292499222617</v>
+        <v>78.4041489140113</v>
       </c>
       <c r="D15">
-        <v>89.02492499222616</v>
+        <v>89.17014891401131</v>
       </c>
       <c r="E15">
-        <v>-30.748</v>
+        <v>-29.844</v>
       </c>
       <c r="F15">
-        <v>11.752</v>
+        <v>12.656</v>
       </c>
       <c r="G15">
         <v>1.89</v>
@@ -2636,28 +2636,28 @@
         <v>12.35</v>
       </c>
       <c r="M15">
-        <v>0.5911256</v>
+        <v>0.6365968000000001</v>
       </c>
       <c r="N15">
-        <v>11.7588744</v>
+        <v>11.7134032</v>
       </c>
       <c r="O15">
-        <v>2.35177488</v>
+        <v>2.34268064</v>
       </c>
       <c r="P15">
-        <v>9.407099519999999</v>
+        <v>9.370722560000001</v>
       </c>
       <c r="Q15">
-        <v>9.807099519999998</v>
+        <v>9.770722559999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08994131151751877</v>
+        <v>0.09036288939362325</v>
       </c>
       <c r="T15">
-        <v>0.8603963216563626</v>
+        <v>0.868613659144127</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.89234504477559</v>
+        <v>19.40003468443448</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.083345684878516</v>
+        <v>0.08321122873679065</v>
       </c>
       <c r="C16">
-        <v>78.4041489140113</v>
+        <v>77.64584740956761</v>
       </c>
       <c r="D16">
-        <v>89.17014891401131</v>
+        <v>89.31584740956761</v>
       </c>
       <c r="E16">
-        <v>-29.844</v>
+        <v>-28.94</v>
       </c>
       <c r="F16">
-        <v>12.656</v>
+        <v>13.56</v>
       </c>
       <c r="G16">
         <v>1.89</v>
@@ -2718,28 +2718,28 @@
         <v>12.35</v>
       </c>
       <c r="M16">
-        <v>0.6365968000000001</v>
+        <v>0.6820680000000001</v>
       </c>
       <c r="N16">
-        <v>11.7134032</v>
+        <v>11.667932</v>
       </c>
       <c r="O16">
-        <v>2.34268064</v>
+        <v>2.3335864</v>
       </c>
       <c r="P16">
-        <v>9.370722560000001</v>
+        <v>9.334345600000001</v>
       </c>
       <c r="Q16">
-        <v>9.770722559999999</v>
+        <v>9.734345599999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09036288939362325</v>
+        <v>0.09079438674916547</v>
       </c>
       <c r="T16">
-        <v>0.868613659144127</v>
+        <v>0.8770243457492505</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.40003468443448</v>
+        <v>18.10669903880551</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08321122873679065</v>
+        <v>0.0830767725950653</v>
       </c>
       <c r="C17">
-        <v>77.64584740956761</v>
+        <v>76.88802280897468</v>
       </c>
       <c r="D17">
-        <v>89.31584740956761</v>
+        <v>89.46202280897468</v>
       </c>
       <c r="E17">
-        <v>-28.94</v>
+        <v>-28.036</v>
       </c>
       <c r="F17">
-        <v>13.56</v>
+        <v>14.464</v>
       </c>
       <c r="G17">
         <v>1.89</v>
@@ -2800,28 +2800,28 @@
         <v>12.35</v>
       </c>
       <c r="M17">
-        <v>0.682068</v>
+        <v>0.7275391999999999</v>
       </c>
       <c r="N17">
-        <v>11.667932</v>
+        <v>11.6224608</v>
       </c>
       <c r="O17">
-        <v>2.3335864</v>
+        <v>2.32449216</v>
       </c>
       <c r="P17">
-        <v>9.334345600000001</v>
+        <v>9.297968639999999</v>
       </c>
       <c r="Q17">
-        <v>9.734345599999999</v>
+        <v>9.697968639999997</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09079438674916547</v>
+        <v>0.09123615785126822</v>
       </c>
       <c r="T17">
-        <v>0.8770243457492505</v>
+        <v>0.885635286797353</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.10669903880552</v>
+        <v>16.97503034888017</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0830767725950653</v>
+        <v>0.08294231645333995</v>
       </c>
       <c r="C18">
-        <v>76.88802280897468</v>
+        <v>76.13067745759079</v>
       </c>
       <c r="D18">
-        <v>89.46202280897468</v>
+        <v>89.6086774575908</v>
       </c>
       <c r="E18">
-        <v>-28.036</v>
+        <v>-27.132</v>
       </c>
       <c r="F18">
-        <v>14.464</v>
+        <v>15.368</v>
       </c>
       <c r="G18">
         <v>1.89</v>
@@ -2882,28 +2882,28 @@
         <v>12.35</v>
       </c>
       <c r="M18">
-        <v>0.7275391999999999</v>
+        <v>0.7730104000000001</v>
       </c>
       <c r="N18">
-        <v>11.6224608</v>
+        <v>11.5769896</v>
       </c>
       <c r="O18">
-        <v>2.32449216</v>
+        <v>2.31539792</v>
       </c>
       <c r="P18">
-        <v>9.297968639999999</v>
+        <v>9.261591679999999</v>
       </c>
       <c r="Q18">
-        <v>9.697968639999997</v>
+        <v>9.661591679999997</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09123615785126822</v>
+        <v>0.09168857404016863</v>
       </c>
       <c r="T18">
-        <v>0.885635286797353</v>
+        <v>0.8944537204008316</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.97503034888017</v>
+        <v>15.97649915188722</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08294231645333995</v>
+        <v>0.08280786031161463</v>
       </c>
       <c r="C19">
-        <v>76.13067745759079</v>
+        <v>75.37381371617846</v>
       </c>
       <c r="D19">
-        <v>89.6086774575908</v>
+        <v>89.75581371617847</v>
       </c>
       <c r="E19">
-        <v>-27.132</v>
+        <v>-26.228</v>
       </c>
       <c r="F19">
-        <v>15.368</v>
+        <v>16.272</v>
       </c>
       <c r="G19">
         <v>1.89</v>
@@ -2964,28 +2964,28 @@
         <v>12.35</v>
       </c>
       <c r="M19">
-        <v>0.7730104000000001</v>
+        <v>0.8184816</v>
       </c>
       <c r="N19">
-        <v>11.5769896</v>
+        <v>11.5315184</v>
       </c>
       <c r="O19">
-        <v>2.31539792</v>
+        <v>2.30630368</v>
       </c>
       <c r="P19">
-        <v>9.261591679999999</v>
+        <v>9.22521472</v>
       </c>
       <c r="Q19">
-        <v>9.661591679999997</v>
+        <v>9.625214719999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09168857404016863</v>
+        <v>0.09215202477026174</v>
       </c>
       <c r="T19">
-        <v>0.8944537204008316</v>
+        <v>0.9034872377507367</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.97649915188722</v>
+        <v>15.08891586567126</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08280786031161463</v>
+        <v>0.08267340416988929</v>
       </c>
       <c r="C20">
-        <v>75.37381371617846</v>
+        <v>74.61743396103113</v>
       </c>
       <c r="D20">
-        <v>89.75581371617847</v>
+        <v>89.90343396103113</v>
       </c>
       <c r="E20">
-        <v>-26.228</v>
+        <v>-25.324</v>
       </c>
       <c r="F20">
-        <v>16.272</v>
+        <v>17.176</v>
       </c>
       <c r="G20">
         <v>1.89</v>
@@ -3046,28 +3046,28 @@
         <v>12.35</v>
       </c>
       <c r="M20">
-        <v>0.8184816</v>
+        <v>0.8639528000000001</v>
       </c>
       <c r="N20">
-        <v>11.5315184</v>
+        <v>11.4860472</v>
       </c>
       <c r="O20">
-        <v>2.30630368</v>
+        <v>2.29720944</v>
       </c>
       <c r="P20">
-        <v>9.22521472</v>
+        <v>9.18883776</v>
       </c>
       <c r="Q20">
-        <v>9.625214719999999</v>
+        <v>9.588837759999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09215202477026174</v>
+        <v>0.09262691872825837</v>
       </c>
       <c r="T20">
-        <v>0.9034872377507365</v>
+        <v>0.9127438049117502</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.08891586567126</v>
+        <v>14.29476239905698</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08267340416988929</v>
+        <v>0.08253894802816394</v>
       </c>
       <c r="C21">
-        <v>74.61743396103113</v>
+        <v>73.86154058410092</v>
       </c>
       <c r="D21">
-        <v>89.90343396103113</v>
+        <v>90.05154058410092</v>
       </c>
       <c r="E21">
-        <v>-25.324</v>
+        <v>-24.42</v>
       </c>
       <c r="F21">
-        <v>17.176</v>
+        <v>18.08</v>
       </c>
       <c r="G21">
         <v>1.89</v>
@@ -3128,28 +3128,28 @@
         <v>12.35</v>
       </c>
       <c r="M21">
-        <v>0.8639528000000001</v>
+        <v>0.909424</v>
       </c>
       <c r="N21">
-        <v>11.4860472</v>
+        <v>11.440576</v>
       </c>
       <c r="O21">
-        <v>2.29720944</v>
+        <v>2.2881152</v>
       </c>
       <c r="P21">
-        <v>9.18883776</v>
+        <v>9.1524608</v>
       </c>
       <c r="Q21">
-        <v>9.588837759999999</v>
+        <v>9.552460799999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09262691872825837</v>
+        <v>0.09311368503520492</v>
       </c>
       <c r="T21">
-        <v>0.9127438049117502</v>
+        <v>0.9222317862517891</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.29476239905698</v>
+        <v>13.58002427910414</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08253894802816394</v>
+        <v>0.0824044918864386</v>
       </c>
       <c r="C22">
-        <v>73.86154058410092</v>
+        <v>73.10613599312799</v>
       </c>
       <c r="D22">
-        <v>90.05154058410092</v>
+        <v>90.200135993128</v>
       </c>
       <c r="E22">
-        <v>-24.42</v>
+        <v>-23.516</v>
       </c>
       <c r="F22">
-        <v>18.08</v>
+        <v>18.984</v>
       </c>
       <c r="G22">
         <v>1.89</v>
@@ -3210,28 +3210,28 @@
         <v>12.35</v>
       </c>
       <c r="M22">
-        <v>0.909424</v>
+        <v>0.9548952000000001</v>
       </c>
       <c r="N22">
-        <v>11.440576</v>
+        <v>11.3951048</v>
       </c>
       <c r="O22">
-        <v>2.2881152</v>
+        <v>2.27902096</v>
       </c>
       <c r="P22">
-        <v>9.1524608</v>
+        <v>9.11608384</v>
       </c>
       <c r="Q22">
-        <v>9.552460799999999</v>
+        <v>9.516083839999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09311368503520492</v>
+        <v>0.09361277453979569</v>
       </c>
       <c r="T22">
-        <v>0.9222317862517891</v>
+        <v>0.9319599696510696</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.58002427910414</v>
+        <v>12.93335645628965</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0824044918864386</v>
+        <v>0.08253403574471327</v>
       </c>
       <c r="C23">
-        <v>73.10613599312799</v>
+        <v>72.058960820894</v>
       </c>
       <c r="D23">
-        <v>90.200135993128</v>
+        <v>90.05696082089401</v>
       </c>
       <c r="E23">
-        <v>-23.516</v>
+        <v>-22.612</v>
       </c>
       <c r="F23">
-        <v>18.984</v>
+        <v>19.888</v>
       </c>
       <c r="G23">
         <v>1.89</v>
@@ -3292,45 +3292,45 @@
         <v>12.35</v>
       </c>
       <c r="M23">
-        <v>0.9548952000000001</v>
+        <v>1.0301984</v>
       </c>
       <c r="N23">
-        <v>11.3951048</v>
+        <v>11.3198016</v>
       </c>
       <c r="O23">
-        <v>2.27902096</v>
+        <v>2.26396032</v>
       </c>
       <c r="P23">
-        <v>9.11608384</v>
+        <v>9.055841279999999</v>
       </c>
       <c r="Q23">
-        <v>9.516083839999999</v>
+        <v>9.455841279999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09361277453979569</v>
+        <v>0.09412466121117084</v>
       </c>
       <c r="T23">
-        <v>0.9319599696510696</v>
+        <v>0.9419375936503317</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.2</v>
       </c>
       <c r="W23">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.93335645628965</v>
+        <v>11.98798212072548</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08253403574471327</v>
+        <v>0.08241157960298792</v>
       </c>
       <c r="C24">
-        <v>72.058960820894</v>
+        <v>71.2902906966922</v>
       </c>
       <c r="D24">
-        <v>90.05696082089401</v>
+        <v>90.1922906966922</v>
       </c>
       <c r="E24">
-        <v>-22.612</v>
+        <v>-21.708</v>
       </c>
       <c r="F24">
-        <v>19.888</v>
+        <v>20.792</v>
       </c>
       <c r="G24">
         <v>1.89</v>
@@ -3374,28 +3374,28 @@
         <v>12.35</v>
       </c>
       <c r="M24">
-        <v>1.0301984</v>
+        <v>1.0770256</v>
       </c>
       <c r="N24">
-        <v>11.3198016</v>
+        <v>11.2729744</v>
       </c>
       <c r="O24">
-        <v>2.26396032</v>
+        <v>2.25459488</v>
       </c>
       <c r="P24">
-        <v>9.055841279999999</v>
+        <v>9.01837952</v>
       </c>
       <c r="Q24">
-        <v>9.455841279999998</v>
+        <v>9.418379519999998</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09412466121117084</v>
+        <v>0.09464984364024405</v>
       </c>
       <c r="T24">
-        <v>0.9419375936503317</v>
+        <v>0.9521743767145097</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.98798212072548</v>
+        <v>11.4667655067809</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08241157960298792</v>
+        <v>0.08228912346126258</v>
       </c>
       <c r="C25">
-        <v>71.2902906966922</v>
+        <v>70.5220279088585</v>
       </c>
       <c r="D25">
-        <v>90.1922906966922</v>
+        <v>90.3280279088585</v>
       </c>
       <c r="E25">
-        <v>-21.708</v>
+        <v>-20.804</v>
       </c>
       <c r="F25">
-        <v>20.792</v>
+        <v>21.696</v>
       </c>
       <c r="G25">
         <v>1.89</v>
@@ -3456,28 +3456,28 @@
         <v>12.35</v>
       </c>
       <c r="M25">
-        <v>1.0770256</v>
+        <v>1.1238528</v>
       </c>
       <c r="N25">
-        <v>11.2729744</v>
+        <v>11.2261472</v>
       </c>
       <c r="O25">
-        <v>2.25459488</v>
+        <v>2.24522944</v>
       </c>
       <c r="P25">
-        <v>9.01837952</v>
+        <v>8.980917760000001</v>
       </c>
       <c r="Q25">
-        <v>9.418379519999998</v>
+        <v>9.380917759999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09464984364024405</v>
+        <v>0.09518884665955601</v>
       </c>
       <c r="T25">
-        <v>0.9521743767145097</v>
+        <v>0.9626805488066923</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.4667655067809</v>
+        <v>10.98898361066503</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08228912346126258</v>
+        <v>0.08216666731953723</v>
       </c>
       <c r="C26">
-        <v>70.5220279088585</v>
+        <v>69.75417429925903</v>
       </c>
       <c r="D26">
-        <v>90.3280279088585</v>
+        <v>90.46417429925903</v>
       </c>
       <c r="E26">
-        <v>-20.804</v>
+        <v>-19.9</v>
       </c>
       <c r="F26">
-        <v>21.696</v>
+        <v>22.6</v>
       </c>
       <c r="G26">
         <v>1.89</v>
@@ -3538,28 +3538,28 @@
         <v>12.35</v>
       </c>
       <c r="M26">
-        <v>1.1238528</v>
+        <v>1.17068</v>
       </c>
       <c r="N26">
-        <v>11.2261472</v>
+        <v>11.17932</v>
       </c>
       <c r="O26">
-        <v>2.24522944</v>
+        <v>2.235864</v>
       </c>
       <c r="P26">
-        <v>8.980917760000001</v>
+        <v>8.943456000000001</v>
       </c>
       <c r="Q26">
-        <v>9.380917759999999</v>
+        <v>9.343456</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09518884665955601</v>
+        <v>0.09574222309271631</v>
       </c>
       <c r="T26">
-        <v>0.9626805488066921</v>
+        <v>0.9734668854879996</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.98898361066503</v>
+        <v>10.54942426623843</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08216666731953723</v>
+        <v>0.0820442111778119</v>
       </c>
       <c r="C27">
-        <v>69.75417429925903</v>
+        <v>68.98673172088114</v>
       </c>
       <c r="D27">
-        <v>90.46417429925903</v>
+        <v>90.60073172088114</v>
       </c>
       <c r="E27">
-        <v>-19.9</v>
+        <v>-18.996</v>
       </c>
       <c r="F27">
-        <v>22.6</v>
+        <v>23.504</v>
       </c>
       <c r="G27">
         <v>1.89</v>
@@ -3620,28 +3620,28 @@
         <v>12.35</v>
       </c>
       <c r="M27">
-        <v>1.17068</v>
+        <v>1.2175072</v>
       </c>
       <c r="N27">
-        <v>11.17932</v>
+        <v>11.1324928</v>
       </c>
       <c r="O27">
-        <v>2.235864</v>
+        <v>2.22649856</v>
       </c>
       <c r="P27">
-        <v>8.943456000000001</v>
+        <v>8.90599424</v>
       </c>
       <c r="Q27">
-        <v>9.343456</v>
+        <v>9.305994239999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09574222309271631</v>
+        <v>0.09631055564569174</v>
       </c>
       <c r="T27">
-        <v>0.9734668854879996</v>
+        <v>0.9845447447823155</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.54942426623843</v>
+        <v>10.14367717907541</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0820442111778119</v>
+        <v>0.08228895503608656</v>
       </c>
       <c r="C28">
-        <v>68.98673172088114</v>
+        <v>67.81021488206395</v>
       </c>
       <c r="D28">
-        <v>90.60073172088114</v>
+        <v>90.32821488206395</v>
       </c>
       <c r="E28">
-        <v>-18.996</v>
+        <v>-18.092</v>
       </c>
       <c r="F28">
-        <v>23.504</v>
+        <v>24.408</v>
       </c>
       <c r="G28">
         <v>1.89</v>
@@ -3702,45 +3702,45 @@
         <v>12.35</v>
       </c>
       <c r="M28">
-        <v>1.2175072</v>
+        <v>1.305828</v>
       </c>
       <c r="N28">
-        <v>11.1324928</v>
+        <v>11.044172</v>
       </c>
       <c r="O28">
-        <v>2.22649856</v>
+        <v>2.2088344</v>
       </c>
       <c r="P28">
-        <v>8.90599424</v>
+        <v>8.835337599999999</v>
       </c>
       <c r="Q28">
-        <v>9.305994239999999</v>
+        <v>9.235337599999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09631055564569174</v>
+        <v>0.09689445895354323</v>
       </c>
       <c r="T28">
-        <v>0.9845447447823155</v>
+        <v>0.9959261070709962</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>10.14367717907541</v>
+        <v>9.457600847891145</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08228895503608656</v>
+        <v>0.0821800988943612</v>
       </c>
       <c r="C29">
-        <v>67.81021488206395</v>
+        <v>67.02722107667137</v>
       </c>
       <c r="D29">
-        <v>90.32821488206395</v>
+        <v>90.44922107667136</v>
       </c>
       <c r="E29">
-        <v>-18.092</v>
+        <v>-17.188</v>
       </c>
       <c r="F29">
-        <v>24.408</v>
+        <v>25.312</v>
       </c>
       <c r="G29">
         <v>1.89</v>
@@ -3784,28 +3784,28 @@
         <v>12.35</v>
       </c>
       <c r="M29">
-        <v>1.305828</v>
+        <v>1.354192</v>
       </c>
       <c r="N29">
-        <v>11.044172</v>
+        <v>10.995808</v>
       </c>
       <c r="O29">
-        <v>2.2088344</v>
+        <v>2.1991616</v>
       </c>
       <c r="P29">
-        <v>8.835337599999999</v>
+        <v>8.7966464</v>
       </c>
       <c r="Q29">
-        <v>9.235337599999998</v>
+        <v>9.196646399999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09689445895354323</v>
+        <v>0.09749458179772391</v>
       </c>
       <c r="T29">
-        <v>0.9959261070709962</v>
+        <v>1.00762361831214</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.457600847891145</v>
+        <v>9.119829389037889</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0821800988943612</v>
+        <v>0.08207124275263586</v>
       </c>
       <c r="C30">
-        <v>67.02722107667137</v>
+        <v>66.24455191272034</v>
       </c>
       <c r="D30">
-        <v>90.44922107667136</v>
+        <v>90.57055191272035</v>
       </c>
       <c r="E30">
-        <v>-17.188</v>
+        <v>-16.284</v>
       </c>
       <c r="F30">
-        <v>25.312</v>
+        <v>26.216</v>
       </c>
       <c r="G30">
         <v>1.89</v>
@@ -3866,28 +3866,28 @@
         <v>12.35</v>
       </c>
       <c r="M30">
-        <v>1.354192</v>
+        <v>1.402556</v>
       </c>
       <c r="N30">
-        <v>10.995808</v>
+        <v>10.947444</v>
       </c>
       <c r="O30">
-        <v>2.1991616</v>
+        <v>2.1894888</v>
       </c>
       <c r="P30">
-        <v>8.7966464</v>
+        <v>8.7579552</v>
       </c>
       <c r="Q30">
-        <v>9.196646399999999</v>
+        <v>9.157955199999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09749458179772391</v>
+        <v>0.09811160951075473</v>
       </c>
       <c r="T30">
-        <v>1.00762361831214</v>
+        <v>1.019650636912189</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.119829389037889</v>
+        <v>8.805352513553824</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08207124275263586</v>
+        <v>0.08196238661091053</v>
       </c>
       <c r="C31">
-        <v>66.24455191272034</v>
+        <v>65.46220869841203</v>
       </c>
       <c r="D31">
-        <v>90.57055191272035</v>
+        <v>90.69220869841203</v>
       </c>
       <c r="E31">
-        <v>-16.284</v>
+        <v>-15.38</v>
       </c>
       <c r="F31">
-        <v>26.216</v>
+        <v>27.12</v>
       </c>
       <c r="G31">
         <v>1.89</v>
@@ -3948,28 +3948,28 @@
         <v>12.35</v>
       </c>
       <c r="M31">
-        <v>1.402556</v>
+        <v>1.45092</v>
       </c>
       <c r="N31">
-        <v>10.947444</v>
+        <v>10.89908</v>
       </c>
       <c r="O31">
-        <v>2.1894888</v>
+        <v>2.179816</v>
       </c>
       <c r="P31">
-        <v>8.7579552</v>
+        <v>8.719263999999999</v>
       </c>
       <c r="Q31">
-        <v>9.157955199999998</v>
+        <v>9.119263999999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09811160951075473</v>
+        <v>0.09874626658701505</v>
       </c>
       <c r="T31">
-        <v>1.019650636912189</v>
+        <v>1.032021284615098</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.805352513553824</v>
+        <v>8.511840763102033</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08196238661091053</v>
+        <v>0.08185353046918518</v>
       </c>
       <c r="C32">
-        <v>65.46220869841203</v>
+        <v>64.68019274898595</v>
       </c>
       <c r="D32">
-        <v>90.69220869841203</v>
+        <v>90.81419274898595</v>
       </c>
       <c r="E32">
-        <v>-15.38</v>
+        <v>-14.476</v>
       </c>
       <c r="F32">
-        <v>27.12</v>
+        <v>28.024</v>
       </c>
       <c r="G32">
         <v>1.89</v>
@@ -4030,28 +4030,28 @@
         <v>12.35</v>
       </c>
       <c r="M32">
-        <v>1.45092</v>
+        <v>1.499284</v>
       </c>
       <c r="N32">
-        <v>10.89908</v>
+        <v>10.850716</v>
       </c>
       <c r="O32">
-        <v>2.179816</v>
+        <v>2.1701432</v>
       </c>
       <c r="P32">
-        <v>8.719263999999999</v>
+        <v>8.6805728</v>
       </c>
       <c r="Q32">
-        <v>9.119263999999998</v>
+        <v>9.080572799999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09874626658701505</v>
+        <v>0.09939931952055824</v>
       </c>
       <c r="T32">
-        <v>1.032021284615098</v>
+        <v>1.04475050181664</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.511840763102033</v>
+        <v>8.237265254614869</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08185353046918518</v>
+        <v>0.08174467432745984</v>
       </c>
       <c r="C33">
-        <v>64.68019274898595</v>
+        <v>63.89850538676723</v>
       </c>
       <c r="D33">
-        <v>90.81419274898595</v>
+        <v>90.93650538676722</v>
       </c>
       <c r="E33">
-        <v>-14.476</v>
+        <v>-13.572</v>
       </c>
       <c r="F33">
-        <v>28.024</v>
+        <v>28.928</v>
       </c>
       <c r="G33">
         <v>1.89</v>
@@ -4112,28 +4112,28 @@
         <v>12.35</v>
       </c>
       <c r="M33">
-        <v>1.499284</v>
+        <v>1.547648</v>
       </c>
       <c r="N33">
-        <v>10.850716</v>
+        <v>10.802352</v>
       </c>
       <c r="O33">
-        <v>2.1701432</v>
+        <v>2.1604704</v>
       </c>
       <c r="P33">
-        <v>8.6805728</v>
+        <v>8.6418816</v>
       </c>
       <c r="Q33">
-        <v>9.080572799999999</v>
+        <v>9.041881599999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09939931952055824</v>
+        <v>0.1000715798933233</v>
       </c>
       <c r="T33">
-        <v>1.04475050181664</v>
+        <v>1.057854107759405</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.237265254614869</v>
+        <v>7.979850715408155</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08174467432745984</v>
+        <v>0.08163581818573448</v>
       </c>
       <c r="C34">
-        <v>63.89850538676723</v>
+        <v>63.11714794121454</v>
       </c>
       <c r="D34">
-        <v>90.93650538676722</v>
+        <v>91.05914794121455</v>
       </c>
       <c r="E34">
-        <v>-13.572</v>
+        <v>-12.668</v>
       </c>
       <c r="F34">
-        <v>28.928</v>
+        <v>29.832</v>
       </c>
       <c r="G34">
         <v>1.89</v>
@@ -4194,28 +4194,28 @@
         <v>12.35</v>
       </c>
       <c r="M34">
-        <v>1.547648</v>
+        <v>1.596012</v>
       </c>
       <c r="N34">
-        <v>10.802352</v>
+        <v>10.753988</v>
       </c>
       <c r="O34">
-        <v>2.1604704</v>
+        <v>2.1507976</v>
       </c>
       <c r="P34">
-        <v>8.6418816</v>
+        <v>8.603190399999999</v>
       </c>
       <c r="Q34">
-        <v>9.041881599999998</v>
+        <v>9.003190399999998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1000715798933233</v>
+        <v>0.1007639077399022</v>
       </c>
       <c r="T34">
-        <v>1.057854107759405</v>
+        <v>1.071348866118372</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.979850715408155</v>
+        <v>7.738037057365482</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08163581818573448</v>
+        <v>0.08174456204400915</v>
       </c>
       <c r="C35">
-        <v>63.11714794121454</v>
+        <v>62.0906317204868</v>
       </c>
       <c r="D35">
-        <v>91.05914794121455</v>
+        <v>90.9366317204868</v>
       </c>
       <c r="E35">
-        <v>-12.668</v>
+        <v>-11.764</v>
       </c>
       <c r="F35">
-        <v>29.832</v>
+        <v>30.736</v>
       </c>
       <c r="G35">
         <v>1.89</v>
@@ -4276,45 +4276,45 @@
         <v>12.35</v>
       </c>
       <c r="M35">
-        <v>1.596012</v>
+        <v>1.6689648</v>
       </c>
       <c r="N35">
-        <v>10.753988</v>
+        <v>10.6810352</v>
       </c>
       <c r="O35">
-        <v>2.1507976</v>
+        <v>2.13620704</v>
       </c>
       <c r="P35">
-        <v>8.603190399999999</v>
+        <v>8.54482816</v>
       </c>
       <c r="Q35">
-        <v>9.003190399999998</v>
+        <v>8.944828159999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1007639077399022</v>
+        <v>0.1014772152181957</v>
       </c>
       <c r="T35">
-        <v>1.071348866118372</v>
+        <v>1.085252556548823</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.738037057365482</v>
+        <v>7.399796568507615</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08174456204400915</v>
+        <v>0.08164210590228382</v>
       </c>
       <c r="C36">
-        <v>62.0906317204868</v>
+        <v>61.30205489651424</v>
       </c>
       <c r="D36">
-        <v>90.9366317204868</v>
+        <v>91.05205489651424</v>
       </c>
       <c r="E36">
-        <v>-11.764</v>
+        <v>-10.86</v>
       </c>
       <c r="F36">
-        <v>30.736</v>
+        <v>31.64</v>
       </c>
       <c r="G36">
         <v>1.89</v>
@@ -4358,28 +4358,28 @@
         <v>12.35</v>
       </c>
       <c r="M36">
-        <v>1.6689648</v>
+        <v>1.718052</v>
       </c>
       <c r="N36">
-        <v>10.6810352</v>
+        <v>10.631948</v>
       </c>
       <c r="O36">
-        <v>2.13620704</v>
+        <v>2.1263896</v>
       </c>
       <c r="P36">
-        <v>8.54482816</v>
+        <v>8.5055584</v>
       </c>
       <c r="Q36">
-        <v>8.944828159999998</v>
+        <v>8.905558399999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1014772152181957</v>
+        <v>0.1022124706188982</v>
       </c>
       <c r="T36">
-        <v>1.085252556548823</v>
+        <v>1.099584052838672</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.399796568507615</v>
+        <v>7.188373809407397</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08164210590228382</v>
+        <v>0.08153964976055847</v>
       </c>
       <c r="C37">
-        <v>61.30205489651424</v>
+        <v>60.51377145136318</v>
       </c>
       <c r="D37">
-        <v>91.05205489651424</v>
+        <v>91.16777145136318</v>
       </c>
       <c r="E37">
-        <v>-10.86</v>
+        <v>-9.955999999999996</v>
       </c>
       <c r="F37">
-        <v>31.64</v>
+        <v>32.544</v>
       </c>
       <c r="G37">
         <v>1.89</v>
@@ -4440,28 +4440,28 @@
         <v>12.35</v>
       </c>
       <c r="M37">
-        <v>1.718052</v>
+        <v>1.7671392</v>
       </c>
       <c r="N37">
-        <v>10.631948</v>
+        <v>10.5828608</v>
       </c>
       <c r="O37">
-        <v>2.1263896</v>
+        <v>2.11657216</v>
       </c>
       <c r="P37">
-        <v>8.5055584</v>
+        <v>8.466288639999998</v>
       </c>
       <c r="Q37">
-        <v>8.905558399999999</v>
+        <v>8.866288639999997</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1022124706188982</v>
+        <v>0.1029707027508726</v>
       </c>
       <c r="T37">
-        <v>1.099584052838672</v>
+        <v>1.114363408387579</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.188373809407397</v>
+        <v>6.98869675914608</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08153964976055847</v>
+        <v>0.08143719361883314</v>
       </c>
       <c r="C38">
-        <v>60.51377145136318</v>
+        <v>59.72578250500786</v>
       </c>
       <c r="D38">
-        <v>91.16777145136318</v>
+        <v>91.28378250500786</v>
       </c>
       <c r="E38">
-        <v>-9.955999999999996</v>
+        <v>-9.052</v>
       </c>
       <c r="F38">
-        <v>32.544</v>
+        <v>33.448</v>
       </c>
       <c r="G38">
         <v>1.89</v>
@@ -4522,28 +4522,28 @@
         <v>12.35</v>
       </c>
       <c r="M38">
-        <v>1.7671392</v>
+        <v>1.8162264</v>
       </c>
       <c r="N38">
-        <v>10.5828608</v>
+        <v>10.5337736</v>
       </c>
       <c r="O38">
-        <v>2.11657216</v>
+        <v>2.10675472</v>
       </c>
       <c r="P38">
-        <v>8.466288639999998</v>
+        <v>8.42701888</v>
       </c>
       <c r="Q38">
-        <v>8.866288639999997</v>
+        <v>8.827018879999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1029707027508726</v>
+        <v>0.1037530057441796</v>
       </c>
       <c r="T38">
-        <v>1.114363408387579</v>
+        <v>1.129611949826927</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.98869675914608</v>
+        <v>6.799813062952945</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08143719361883314</v>
+        <v>0.08133473747710779</v>
       </c>
       <c r="C39">
-        <v>59.72578250500786</v>
+        <v>58.93808918313053</v>
       </c>
       <c r="D39">
-        <v>91.28378250500786</v>
+        <v>91.40008918313053</v>
       </c>
       <c r="E39">
-        <v>-9.052</v>
+        <v>-8.147999999999996</v>
       </c>
       <c r="F39">
-        <v>33.448</v>
+        <v>34.352</v>
       </c>
       <c r="G39">
         <v>1.89</v>
@@ -4604,28 +4604,28 @@
         <v>12.35</v>
       </c>
       <c r="M39">
-        <v>1.8162264</v>
+        <v>1.8653136</v>
       </c>
       <c r="N39">
-        <v>10.5337736</v>
+        <v>10.4846864</v>
       </c>
       <c r="O39">
-        <v>2.10675472</v>
+        <v>2.09693728</v>
       </c>
       <c r="P39">
-        <v>8.42701888</v>
+        <v>8.387749119999999</v>
       </c>
       <c r="Q39">
-        <v>8.827018879999999</v>
+        <v>8.787749119999997</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1037530057441796</v>
+        <v>0.1045605443179158</v>
       </c>
       <c r="T39">
-        <v>1.129611949826927</v>
+        <v>1.145352379699803</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.799813062952945</v>
+        <v>6.620870613927866</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08133473747710779</v>
+        <v>0.08123228133538245</v>
       </c>
       <c r="C40">
-        <v>58.93808918313053</v>
+        <v>58.1506926171577</v>
       </c>
       <c r="D40">
-        <v>91.40008918313053</v>
+        <v>91.5166926171577</v>
       </c>
       <c r="E40">
-        <v>-8.147999999999996</v>
+        <v>-7.244</v>
       </c>
       <c r="F40">
-        <v>34.352</v>
+        <v>35.256</v>
       </c>
       <c r="G40">
         <v>1.89</v>
@@ -4686,28 +4686,28 @@
         <v>12.35</v>
       </c>
       <c r="M40">
-        <v>1.8653136</v>
+        <v>1.9144008</v>
       </c>
       <c r="N40">
-        <v>10.4846864</v>
+        <v>10.4355992</v>
       </c>
       <c r="O40">
-        <v>2.09693728</v>
+        <v>2.08711984</v>
       </c>
       <c r="P40">
-        <v>8.387749119999999</v>
+        <v>8.348479359999999</v>
       </c>
       <c r="Q40">
-        <v>8.787749119999997</v>
+        <v>8.748479359999997</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1045605443179158</v>
+        <v>0.1053945595662007</v>
       </c>
       <c r="T40">
-        <v>1.145352379699803</v>
+        <v>1.161608889240642</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.620870613927866</v>
+        <v>6.451104700750228</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08123228133538245</v>
+        <v>0.08112982519365712</v>
       </c>
       <c r="C41">
-        <v>58.1506926171577</v>
+        <v>57.36359394429697</v>
       </c>
       <c r="D41">
-        <v>91.5166926171577</v>
+        <v>91.63359394429698</v>
       </c>
       <c r="E41">
-        <v>-7.244</v>
+        <v>-6.339999999999996</v>
       </c>
       <c r="F41">
-        <v>35.256</v>
+        <v>36.16</v>
       </c>
       <c r="G41">
         <v>1.89</v>
@@ -4768,28 +4768,28 @@
         <v>12.35</v>
       </c>
       <c r="M41">
-        <v>1.9144008</v>
+        <v>1.963488</v>
       </c>
       <c r="N41">
-        <v>10.4355992</v>
+        <v>10.386512</v>
       </c>
       <c r="O41">
-        <v>2.08711984</v>
+        <v>2.0773024</v>
       </c>
       <c r="P41">
-        <v>8.348479359999999</v>
+        <v>8.309209599999999</v>
       </c>
       <c r="Q41">
-        <v>8.748479359999997</v>
+        <v>8.709209599999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1053945595662007</v>
+        <v>0.1062563753227619</v>
       </c>
       <c r="T41">
-        <v>1.161608889240642</v>
+        <v>1.178407282432842</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.451104700750228</v>
+        <v>6.289827083231473</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08112982519365712</v>
+        <v>0.08102736905193178</v>
       </c>
       <c r="C42">
-        <v>57.36359394429697</v>
+        <v>56.57679430757396</v>
       </c>
       <c r="D42">
-        <v>91.63359394429698</v>
+        <v>91.75079430757397</v>
       </c>
       <c r="E42">
-        <v>-6.339999999999996</v>
+        <v>-5.435999999999993</v>
       </c>
       <c r="F42">
-        <v>36.16</v>
+        <v>37.06400000000001</v>
       </c>
       <c r="G42">
         <v>1.89</v>
@@ -4850,28 +4850,28 @@
         <v>12.35</v>
       </c>
       <c r="M42">
-        <v>1.963488</v>
+        <v>2.012575200000001</v>
       </c>
       <c r="N42">
-        <v>10.386512</v>
+        <v>10.3374248</v>
       </c>
       <c r="O42">
-        <v>2.0773024</v>
+        <v>2.06748496</v>
       </c>
       <c r="P42">
-        <v>8.309209599999999</v>
+        <v>8.269939839999999</v>
       </c>
       <c r="Q42">
-        <v>8.709209599999998</v>
+        <v>8.669939839999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1062563753227619</v>
+        <v>0.1071474051727657</v>
       </c>
       <c r="T42">
-        <v>1.178407282432842</v>
+        <v>1.195775112682405</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.289827083231473</v>
+        <v>6.13641666656729</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08102736905193178</v>
+        <v>0.08126091291020643</v>
       </c>
       <c r="C43">
-        <v>56.57679430757396</v>
+        <v>55.40607761032159</v>
       </c>
       <c r="D43">
-        <v>91.75079430757397</v>
+        <v>91.48407761032159</v>
       </c>
       <c r="E43">
-        <v>-5.435999999999993</v>
+        <v>-4.531999999999996</v>
       </c>
       <c r="F43">
-        <v>37.06400000000001</v>
+        <v>37.968</v>
       </c>
       <c r="G43">
         <v>1.89</v>
@@ -4932,45 +4932,45 @@
         <v>12.35</v>
       </c>
       <c r="M43">
-        <v>2.012575200000001</v>
+        <v>2.0996304</v>
       </c>
       <c r="N43">
-        <v>10.3374248</v>
+        <v>10.2503696</v>
       </c>
       <c r="O43">
-        <v>2.06748496</v>
+        <v>2.05007392</v>
       </c>
       <c r="P43">
-        <v>8.269939839999999</v>
+        <v>8.20029568</v>
       </c>
       <c r="Q43">
-        <v>8.669939839999998</v>
+        <v>8.600295679999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1071474051727657</v>
+        <v>0.1080691601900111</v>
       </c>
       <c r="T43">
-        <v>1.195775112682405</v>
+        <v>1.213741833630229</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.13641666656729</v>
+        <v>5.881987610771876</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08126091291020643</v>
+        <v>0.0811664567684811</v>
       </c>
       <c r="C44">
-        <v>55.40607761032159</v>
+        <v>54.60976343634644</v>
       </c>
       <c r="D44">
-        <v>91.48407761032159</v>
+        <v>91.59176343634644</v>
       </c>
       <c r="E44">
-        <v>-4.531999999999996</v>
+        <v>-3.628</v>
       </c>
       <c r="F44">
-        <v>37.968</v>
+        <v>38.872</v>
       </c>
       <c r="G44">
         <v>1.89</v>
@@ -5014,28 +5014,28 @@
         <v>12.35</v>
       </c>
       <c r="M44">
-        <v>2.0996304</v>
+        <v>2.1496216</v>
       </c>
       <c r="N44">
-        <v>10.2503696</v>
+        <v>10.2003784</v>
       </c>
       <c r="O44">
-        <v>2.05007392</v>
+        <v>2.04007568</v>
       </c>
       <c r="P44">
-        <v>8.20029568</v>
+        <v>8.160302720000001</v>
       </c>
       <c r="Q44">
-        <v>8.600295679999999</v>
+        <v>8.560302719999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1080691601900111</v>
+        <v>0.1090232574885633</v>
       </c>
       <c r="T44">
-        <v>1.213741833630228</v>
+        <v>1.232338965839379</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.881987610771876</v>
+        <v>5.745197201219042</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0811664567684811</v>
+        <v>0.08107200062675574</v>
       </c>
       <c r="C45">
-        <v>54.60976343634644</v>
+        <v>53.81370307491306</v>
       </c>
       <c r="D45">
-        <v>91.59176343634644</v>
+        <v>91.69970307491306</v>
       </c>
       <c r="E45">
-        <v>-3.628</v>
+        <v>-2.723999999999997</v>
       </c>
       <c r="F45">
-        <v>38.872</v>
+        <v>39.776</v>
       </c>
       <c r="G45">
         <v>1.89</v>
@@ -5096,28 +5096,28 @@
         <v>12.35</v>
       </c>
       <c r="M45">
-        <v>2.1496216</v>
+        <v>2.1996128</v>
       </c>
       <c r="N45">
-        <v>10.2003784</v>
+        <v>10.1503872</v>
       </c>
       <c r="O45">
-        <v>2.04007568</v>
+        <v>2.03007744</v>
       </c>
       <c r="P45">
-        <v>8.160302720000001</v>
+        <v>8.12030976</v>
       </c>
       <c r="Q45">
-        <v>8.560302719999999</v>
+        <v>8.520309759999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1090232574885633</v>
+        <v>0.1100114296906352</v>
       </c>
       <c r="T45">
-        <v>1.232338965839379</v>
+        <v>1.251600281341714</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.745197201219042</v>
+        <v>5.614624537554972</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08107200062675574</v>
+        <v>0.0809775444850304</v>
       </c>
       <c r="C46">
-        <v>53.81370307491306</v>
+        <v>53.01789742442392</v>
       </c>
       <c r="D46">
-        <v>91.69970307491306</v>
+        <v>91.80789742442393</v>
       </c>
       <c r="E46">
-        <v>-2.723999999999997</v>
+        <v>-1.819999999999993</v>
       </c>
       <c r="F46">
-        <v>39.776</v>
+        <v>40.68000000000001</v>
       </c>
       <c r="G46">
         <v>1.89</v>
@@ -5178,28 +5178,28 @@
         <v>12.35</v>
       </c>
       <c r="M46">
-        <v>2.1996128</v>
+        <v>2.249604000000001</v>
       </c>
       <c r="N46">
-        <v>10.1503872</v>
+        <v>10.100396</v>
       </c>
       <c r="O46">
-        <v>2.03007744</v>
+        <v>2.0200792</v>
       </c>
       <c r="P46">
-        <v>8.12030976</v>
+        <v>8.0803168</v>
       </c>
       <c r="Q46">
-        <v>8.520309759999998</v>
+        <v>8.480316799999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1100114296906352</v>
+        <v>0.111035535427328</v>
       </c>
       <c r="T46">
-        <v>1.251600281341714</v>
+        <v>1.271562008316861</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.614624537554972</v>
+        <v>5.489855103387084</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0809775444850304</v>
+        <v>0.08088308834330507</v>
       </c>
       <c r="C47">
-        <v>53.01789742442392</v>
+        <v>52.22234738752671</v>
       </c>
       <c r="D47">
-        <v>91.80789742442393</v>
+        <v>91.91634738752671</v>
       </c>
       <c r="E47">
-        <v>-1.819999999999993</v>
+        <v>-0.9159999999999968</v>
       </c>
       <c r="F47">
-        <v>40.68000000000001</v>
+        <v>41.584</v>
       </c>
       <c r="G47">
         <v>1.89</v>
@@ -5260,28 +5260,28 @@
         <v>12.35</v>
       </c>
       <c r="M47">
-        <v>2.249604000000001</v>
+        <v>2.2995952</v>
       </c>
       <c r="N47">
-        <v>10.100396</v>
+        <v>10.0504048</v>
       </c>
       <c r="O47">
-        <v>2.0200792</v>
+        <v>2.01008096</v>
       </c>
       <c r="P47">
-        <v>8.0803168</v>
+        <v>8.040323839999999</v>
       </c>
       <c r="Q47">
-        <v>8.480316799999999</v>
+        <v>8.440323839999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.111035535427328</v>
+        <v>0.1120975710061205</v>
       </c>
       <c r="T47">
-        <v>1.271562008316861</v>
+        <v>1.29226305851331</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.489855103387084</v>
+        <v>5.370510427226495</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08088308834330507</v>
+        <v>0.08078863220157972</v>
       </c>
       <c r="C48">
-        <v>52.22234738752671</v>
+        <v>51.42705387113912</v>
       </c>
       <c r="D48">
-        <v>91.91634738752671</v>
+        <v>92.02505387113912</v>
       </c>
       <c r="E48">
-        <v>-0.9159999999999968</v>
+        <v>-0.01199999999999335</v>
       </c>
       <c r="F48">
-        <v>41.584</v>
+        <v>42.48800000000001</v>
       </c>
       <c r="G48">
         <v>1.89</v>
@@ -5342,28 +5342,28 @@
         <v>12.35</v>
       </c>
       <c r="M48">
-        <v>2.2995952</v>
+        <v>2.349586400000001</v>
       </c>
       <c r="N48">
-        <v>10.0504048</v>
+        <v>10.0004136</v>
       </c>
       <c r="O48">
-        <v>2.01008096</v>
+        <v>2.00008272</v>
       </c>
       <c r="P48">
-        <v>8.040323839999999</v>
+        <v>8.000330879999998</v>
       </c>
       <c r="Q48">
-        <v>8.440323839999998</v>
+        <v>8.400330879999997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1120975710061205</v>
+        <v>0.113199683399207</v>
       </c>
       <c r="T48">
-        <v>1.29226305851331</v>
+        <v>1.313745280415285</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.370510427226495</v>
+        <v>5.256244247923803</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08078863220157972</v>
+        <v>0.08069417605985438</v>
       </c>
       <c r="C49">
-        <v>51.42705387113912</v>
+        <v>50.63201778647424</v>
       </c>
       <c r="D49">
-        <v>92.02505387113912</v>
+        <v>92.13401778647425</v>
       </c>
       <c r="E49">
-        <v>-0.01199999999999335</v>
+        <v>0.892000000000003</v>
       </c>
       <c r="F49">
-        <v>42.48800000000001</v>
+        <v>43.392</v>
       </c>
       <c r="G49">
         <v>1.89</v>
@@ -5424,28 +5424,28 @@
         <v>12.35</v>
       </c>
       <c r="M49">
-        <v>2.349586400000001</v>
+        <v>2.3995776</v>
       </c>
       <c r="N49">
-        <v>10.0004136</v>
+        <v>9.950422399999999</v>
       </c>
       <c r="O49">
-        <v>2.00008272</v>
+        <v>1.99008448</v>
       </c>
       <c r="P49">
-        <v>8.000330879999998</v>
+        <v>7.960337919999999</v>
       </c>
       <c r="Q49">
-        <v>8.400330879999997</v>
+        <v>8.360337919999997</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.113199683399207</v>
+        <v>0.1143441847304892</v>
       </c>
       <c r="T49">
-        <v>1.313745280415285</v>
+        <v>1.336053741621182</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.256244247923803</v>
+        <v>5.146739159425391</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08069417605985438</v>
+        <v>0.08059971991812903</v>
       </c>
       <c r="C50">
-        <v>50.63201778647424</v>
+        <v>49.83724004906615</v>
       </c>
       <c r="D50">
-        <v>92.13401778647425</v>
+        <v>92.24324004906615</v>
       </c>
       <c r="E50">
-        <v>0.892000000000003</v>
+        <v>1.795999999999999</v>
       </c>
       <c r="F50">
-        <v>43.392</v>
+        <v>44.296</v>
       </c>
       <c r="G50">
         <v>1.89</v>
@@ -5506,28 +5506,28 @@
         <v>12.35</v>
       </c>
       <c r="M50">
-        <v>2.3995776</v>
+        <v>2.4495688</v>
       </c>
       <c r="N50">
-        <v>9.950422399999999</v>
+        <v>9.9004312</v>
       </c>
       <c r="O50">
-        <v>1.99008448</v>
+        <v>1.98008624</v>
       </c>
       <c r="P50">
-        <v>7.960337919999999</v>
+        <v>7.92034496</v>
       </c>
       <c r="Q50">
-        <v>8.360337919999997</v>
+        <v>8.320344959999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1143441847304892</v>
+        <v>0.1155335684669197</v>
       </c>
       <c r="T50">
-        <v>1.336053741621182</v>
+        <v>1.359237044442996</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.146739159425391</v>
+        <v>5.041703666375894</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08059971991812903</v>
+        <v>0.0805052637764037</v>
       </c>
       <c r="C51">
-        <v>49.83724004906615</v>
+        <v>49.04272157879527</v>
       </c>
       <c r="D51">
-        <v>92.24324004906615</v>
+        <v>92.35272157879527</v>
       </c>
       <c r="E51">
-        <v>1.795999999999999</v>
+        <v>2.700000000000003</v>
       </c>
       <c r="F51">
-        <v>44.296</v>
+        <v>45.2</v>
       </c>
       <c r="G51">
         <v>1.89</v>
@@ -5588,28 +5588,28 @@
         <v>12.35</v>
       </c>
       <c r="M51">
-        <v>2.4495688</v>
+        <v>2.49956</v>
       </c>
       <c r="N51">
-        <v>9.9004312</v>
+        <v>9.850439999999999</v>
       </c>
       <c r="O51">
-        <v>1.98008624</v>
+        <v>1.970088</v>
       </c>
       <c r="P51">
-        <v>7.92034496</v>
+        <v>7.880351999999999</v>
       </c>
       <c r="Q51">
-        <v>8.320344959999998</v>
+        <v>8.280351999999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1155335684669197</v>
+        <v>0.1167705275528074</v>
       </c>
       <c r="T51">
-        <v>1.359237044442996</v>
+        <v>1.383347679377684</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.041703666375894</v>
+        <v>4.940869593048376</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0805052637764037</v>
+        <v>0.08041080763467835</v>
       </c>
       <c r="C52">
-        <v>49.04272157879527</v>
+        <v>48.24846329991448</v>
       </c>
       <c r="D52">
-        <v>92.35272157879527</v>
+        <v>92.46246329991449</v>
       </c>
       <c r="E52">
-        <v>2.700000000000003</v>
+        <v>3.604000000000006</v>
       </c>
       <c r="F52">
-        <v>45.2</v>
+        <v>46.10400000000001</v>
       </c>
       <c r="G52">
         <v>1.89</v>
@@ -5670,28 +5670,28 @@
         <v>12.35</v>
       </c>
       <c r="M52">
-        <v>2.49956</v>
+        <v>2.5495512</v>
       </c>
       <c r="N52">
-        <v>9.850439999999999</v>
+        <v>9.8004488</v>
       </c>
       <c r="O52">
-        <v>1.970088</v>
+        <v>1.96008976</v>
       </c>
       <c r="P52">
-        <v>7.880351999999999</v>
+        <v>7.84035904</v>
       </c>
       <c r="Q52">
-        <v>8.280351999999997</v>
+        <v>8.240359039999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1167705275528074</v>
+        <v>0.1180579747646497</v>
       </c>
       <c r="T52">
-        <v>1.383347679377684</v>
+        <v>1.408442421860726</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.940869593048376</v>
+        <v>4.843989797106251</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08041080763467835</v>
+        <v>0.08031635149295301</v>
       </c>
       <c r="C53">
-        <v>48.24846329991448</v>
+        <v>47.454466141075</v>
       </c>
       <c r="D53">
-        <v>92.46246329991449</v>
+        <v>92.572466141075</v>
       </c>
       <c r="E53">
-        <v>3.604000000000006</v>
+        <v>4.508000000000003</v>
       </c>
       <c r="F53">
-        <v>46.10400000000001</v>
+        <v>47.008</v>
       </c>
       <c r="G53">
         <v>1.89</v>
@@ -5752,28 +5752,28 @@
         <v>12.35</v>
       </c>
       <c r="M53">
-        <v>2.5495512</v>
+        <v>2.5995424</v>
       </c>
       <c r="N53">
-        <v>9.8004488</v>
+        <v>9.750457599999999</v>
       </c>
       <c r="O53">
-        <v>1.96008976</v>
+        <v>1.95009152</v>
       </c>
       <c r="P53">
-        <v>7.84035904</v>
+        <v>7.800366079999999</v>
       </c>
       <c r="Q53">
-        <v>8.240359039999998</v>
+        <v>8.200366079999998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1180579747646497</v>
+        <v>0.1193990656103188</v>
       </c>
       <c r="T53">
-        <v>1.408442421860726</v>
+        <v>1.434582778613894</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5790,7 +5790,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.843989797106251</v>
+        <v>4.7508361471619</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08031635149295301</v>
+        <v>0.08022189535122767</v>
       </c>
       <c r="C54">
-        <v>47.454466141075</v>
+        <v>46.6607310353525</v>
       </c>
       <c r="D54">
-        <v>92.572466141075</v>
+        <v>92.6827310353525</v>
       </c>
       <c r="E54">
-        <v>4.508000000000003</v>
+        <v>5.412000000000006</v>
       </c>
       <c r="F54">
-        <v>47.008</v>
+        <v>47.91200000000001</v>
       </c>
       <c r="G54">
         <v>1.89</v>
@@ -5834,28 +5834,28 @@
         <v>12.35</v>
       </c>
       <c r="M54">
-        <v>2.5995424</v>
+        <v>2.6495336</v>
       </c>
       <c r="N54">
-        <v>9.750457599999999</v>
+        <v>9.7004664</v>
       </c>
       <c r="O54">
-        <v>1.95009152</v>
+        <v>1.94009328</v>
       </c>
       <c r="P54">
-        <v>7.800366079999999</v>
+        <v>7.76037312</v>
       </c>
       <c r="Q54">
-        <v>8.200366079999998</v>
+        <v>8.160373119999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1193990656103188</v>
+        <v>0.1207972241515483</v>
       </c>
       <c r="T54">
-        <v>1.434582778613894</v>
+        <v>1.461835490973581</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.7508361471619</v>
+        <v>4.661197729290921</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08022189535122767</v>
+        <v>0.08012743920950233</v>
       </c>
       <c r="C55">
-        <v>46.6607310353525</v>
+        <v>45.86725892027368</v>
       </c>
       <c r="D55">
-        <v>92.6827310353525</v>
+        <v>92.79325892027369</v>
       </c>
       <c r="E55">
-        <v>5.412000000000006</v>
+        <v>6.31600000000001</v>
       </c>
       <c r="F55">
-        <v>47.91200000000001</v>
+        <v>48.81600000000001</v>
       </c>
       <c r="G55">
         <v>1.89</v>
@@ -5916,28 +5916,28 @@
         <v>12.35</v>
       </c>
       <c r="M55">
-        <v>2.6495336</v>
+        <v>2.699524800000001</v>
       </c>
       <c r="N55">
-        <v>9.7004664</v>
+        <v>9.650475199999999</v>
       </c>
       <c r="O55">
-        <v>1.94009328</v>
+        <v>1.93009504</v>
       </c>
       <c r="P55">
-        <v>7.76037312</v>
+        <v>7.720380159999999</v>
       </c>
       <c r="Q55">
-        <v>8.160373119999999</v>
+        <v>8.120380159999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1207972241515483</v>
+        <v>0.1222561721945703</v>
       </c>
       <c r="T55">
-        <v>1.461835490973581</v>
+        <v>1.490273103870645</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.661197729290921</v>
+        <v>4.574879252822569</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08012743920950233</v>
+        <v>0.08113298306777698</v>
       </c>
       <c r="C56">
-        <v>45.86725892027368</v>
+        <v>43.79998638428857</v>
       </c>
       <c r="D56">
-        <v>92.79325892027369</v>
+        <v>91.62998638428857</v>
       </c>
       <c r="E56">
-        <v>6.31600000000001</v>
+        <v>7.220000000000006</v>
       </c>
       <c r="F56">
-        <v>48.81600000000001</v>
+        <v>49.72000000000001</v>
       </c>
       <c r="G56">
         <v>1.89</v>
@@ -5998,45 +5998,45 @@
         <v>12.35</v>
       </c>
       <c r="M56">
-        <v>2.699524800000001</v>
+        <v>2.873816000000001</v>
       </c>
       <c r="N56">
-        <v>9.650475199999999</v>
+        <v>9.476184</v>
       </c>
       <c r="O56">
-        <v>1.93009504</v>
+        <v>1.8952368</v>
       </c>
       <c r="P56">
-        <v>7.720380159999999</v>
+        <v>7.5809472</v>
       </c>
       <c r="Q56">
-        <v>8.120380159999998</v>
+        <v>7.980947199999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1222561721945703</v>
+        <v>0.1237799623728378</v>
       </c>
       <c r="T56">
-        <v>1.490273103870645</v>
+        <v>1.519974610674245</v>
       </c>
       <c r="U56">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.2</v>
       </c>
       <c r="W56">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.574879252822569</v>
+        <v>4.297421964384636</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08113298306777698</v>
+        <v>0.08105852692605166</v>
       </c>
       <c r="C57">
-        <v>43.79998638428857</v>
+        <v>42.9811208666771</v>
       </c>
       <c r="D57">
-        <v>91.62998638428857</v>
+        <v>91.71512086667711</v>
       </c>
       <c r="E57">
-        <v>7.220000000000006</v>
+        <v>8.124000000000009</v>
       </c>
       <c r="F57">
-        <v>49.72000000000001</v>
+        <v>50.62400000000001</v>
       </c>
       <c r="G57">
         <v>1.89</v>
@@ -6080,28 +6080,28 @@
         <v>12.35</v>
       </c>
       <c r="M57">
-        <v>2.873816000000001</v>
+        <v>2.926067200000001</v>
       </c>
       <c r="N57">
-        <v>9.476184</v>
+        <v>9.423932799999999</v>
       </c>
       <c r="O57">
-        <v>1.8952368</v>
+        <v>1.88478656</v>
       </c>
       <c r="P57">
-        <v>7.5809472</v>
+        <v>7.539146239999999</v>
       </c>
       <c r="Q57">
-        <v>7.980947199999998</v>
+        <v>7.939146239999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1237799623728378</v>
+        <v>0.1253730157410265</v>
       </c>
       <c r="T57">
-        <v>1.519974610674245</v>
+        <v>1.551026185968919</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.297421964384636</v>
+        <v>4.220682286449196</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08105852692605166</v>
+        <v>0.0809840707843263</v>
       </c>
       <c r="C58">
-        <v>42.9811208666771</v>
+        <v>42.16241369505543</v>
       </c>
       <c r="D58">
-        <v>91.71512086667711</v>
+        <v>91.80041369505544</v>
       </c>
       <c r="E58">
-        <v>8.124000000000009</v>
+        <v>9.028000000000006</v>
       </c>
       <c r="F58">
-        <v>50.62400000000001</v>
+        <v>51.52800000000001</v>
       </c>
       <c r="G58">
         <v>1.89</v>
@@ -6162,28 +6162,28 @@
         <v>12.35</v>
       </c>
       <c r="M58">
-        <v>2.926067200000001</v>
+        <v>2.9783184</v>
       </c>
       <c r="N58">
-        <v>9.423932799999999</v>
+        <v>9.371681599999999</v>
       </c>
       <c r="O58">
-        <v>1.88478656</v>
+        <v>1.87433632</v>
       </c>
       <c r="P58">
-        <v>7.539146239999999</v>
+        <v>7.497345279999999</v>
       </c>
       <c r="Q58">
-        <v>7.939146239999998</v>
+        <v>7.897345279999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1253730157410265</v>
+        <v>0.1270401646147123</v>
       </c>
       <c r="T58">
-        <v>1.551026185968919</v>
+        <v>1.583522020579623</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.220682286449196</v>
+        <v>4.146635228792192</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0809840707843263</v>
+        <v>0.08090961464260096</v>
       </c>
       <c r="C59">
-        <v>42.16241369505543</v>
+        <v>41.3438653116085</v>
       </c>
       <c r="D59">
-        <v>91.80041369505544</v>
+        <v>91.88586531160851</v>
       </c>
       <c r="E59">
-        <v>9.028000000000006</v>
+        <v>9.932000000000009</v>
       </c>
       <c r="F59">
-        <v>51.52800000000001</v>
+        <v>52.43200000000001</v>
       </c>
       <c r="G59">
         <v>1.89</v>
@@ -6244,28 +6244,28 @@
         <v>12.35</v>
       </c>
       <c r="M59">
-        <v>2.9783184</v>
+        <v>3.030569600000001</v>
       </c>
       <c r="N59">
-        <v>9.371681599999999</v>
+        <v>9.319430399999998</v>
       </c>
       <c r="O59">
-        <v>1.87433632</v>
+        <v>1.86388608</v>
       </c>
       <c r="P59">
-        <v>7.497345279999999</v>
+        <v>7.455544319999999</v>
       </c>
       <c r="Q59">
-        <v>7.897345279999998</v>
+        <v>7.855544319999997</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1270401646147123</v>
+        <v>0.1287867015300023</v>
       </c>
       <c r="T59">
-        <v>1.583522020579623</v>
+        <v>1.617565275886075</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.146635228792192</v>
+        <v>4.075141517950948</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08090961464260096</v>
+        <v>0.08083515850087562</v>
       </c>
       <c r="C60">
-        <v>41.34386531160851</v>
+        <v>40.52547616016921</v>
       </c>
       <c r="D60">
-        <v>91.88586531160851</v>
+        <v>91.9714761601692</v>
       </c>
       <c r="E60">
-        <v>9.932000000000002</v>
+        <v>10.836</v>
       </c>
       <c r="F60">
-        <v>52.432</v>
+        <v>53.336</v>
       </c>
       <c r="G60">
         <v>1.89</v>
@@ -6326,28 +6326,28 @@
         <v>12.35</v>
       </c>
       <c r="M60">
-        <v>3.0305696</v>
+        <v>3.0828208</v>
       </c>
       <c r="N60">
-        <v>9.3194304</v>
+        <v>9.267179199999999</v>
       </c>
       <c r="O60">
-        <v>1.86388608</v>
+        <v>1.85343584</v>
       </c>
       <c r="P60">
-        <v>7.45554432</v>
+        <v>7.41374336</v>
       </c>
       <c r="Q60">
-        <v>7.855544319999998</v>
+        <v>7.813743359999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1287867015300023</v>
+        <v>0.1306184353679893</v>
       </c>
       <c r="T60">
-        <v>1.617565275886074</v>
+        <v>1.653269177792842</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.075141517950948</v>
+        <v>4.006071322731441</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08083515850087562</v>
+        <v>0.08244070235915028</v>
       </c>
       <c r="C61">
-        <v>40.52547616016921</v>
+        <v>37.81006943543405</v>
       </c>
       <c r="D61">
-        <v>91.9714761601692</v>
+        <v>90.16006943543405</v>
       </c>
       <c r="E61">
-        <v>10.836</v>
+        <v>11.74</v>
       </c>
       <c r="F61">
-        <v>53.336</v>
+        <v>54.24</v>
       </c>
       <c r="G61">
         <v>1.89</v>
@@ -6408,45 +6408,45 @@
         <v>12.35</v>
       </c>
       <c r="M61">
-        <v>3.0828208</v>
+        <v>3.324912</v>
       </c>
       <c r="N61">
-        <v>9.267179199999999</v>
+        <v>9.025088</v>
       </c>
       <c r="O61">
-        <v>1.85343584</v>
+        <v>1.8050176</v>
       </c>
       <c r="P61">
-        <v>7.41374336</v>
+        <v>7.2200704</v>
       </c>
       <c r="Q61">
-        <v>7.813743359999998</v>
+        <v>7.620070399999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1306184353679893</v>
+        <v>0.1325417558978757</v>
       </c>
       <c r="T61">
-        <v>1.653269177792842</v>
+        <v>1.690758274794947</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V61">
         <v>0.2</v>
       </c>
       <c r="W61">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.006071322731441</v>
+        <v>3.714384019787591</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08244070235915028</v>
+        <v>0.08239424621742494</v>
       </c>
       <c r="C62">
-        <v>37.81006943543405</v>
+        <v>36.95747919668688</v>
       </c>
       <c r="D62">
-        <v>90.16006943543405</v>
+        <v>90.21147919668688</v>
       </c>
       <c r="E62">
-        <v>11.74</v>
+        <v>12.64400000000001</v>
       </c>
       <c r="F62">
-        <v>54.24</v>
+        <v>55.14400000000001</v>
       </c>
       <c r="G62">
         <v>1.89</v>
@@ -6490,28 +6490,28 @@
         <v>12.35</v>
       </c>
       <c r="M62">
-        <v>3.324912</v>
+        <v>3.3803272</v>
       </c>
       <c r="N62">
-        <v>9.025088</v>
+        <v>8.9696728</v>
       </c>
       <c r="O62">
-        <v>1.8050176</v>
+        <v>1.79393456</v>
       </c>
       <c r="P62">
-        <v>7.2200704</v>
+        <v>7.175738239999999</v>
       </c>
       <c r="Q62">
-        <v>7.620070399999999</v>
+        <v>7.575738239999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1325417558978757</v>
+        <v>0.1345637082498075</v>
       </c>
       <c r="T62">
-        <v>1.690758274794947</v>
+        <v>1.730169889592032</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.714384019787591</v>
+        <v>3.653492478479598</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08239424621742494</v>
+        <v>0.08234779007569959</v>
       </c>
       <c r="C63">
-        <v>36.95747919668688</v>
+        <v>36.10494761963911</v>
       </c>
       <c r="D63">
-        <v>90.21147919668688</v>
+        <v>90.26294761963911</v>
       </c>
       <c r="E63">
-        <v>12.64400000000001</v>
+        <v>13.548</v>
       </c>
       <c r="F63">
-        <v>55.14400000000001</v>
+        <v>56.048</v>
       </c>
       <c r="G63">
         <v>1.89</v>
@@ -6572,28 +6572,28 @@
         <v>12.35</v>
       </c>
       <c r="M63">
-        <v>3.3803272</v>
+        <v>3.4357424</v>
       </c>
       <c r="N63">
-        <v>8.9696728</v>
+        <v>8.914257599999999</v>
       </c>
       <c r="O63">
-        <v>1.79393456</v>
+        <v>1.78285152</v>
       </c>
       <c r="P63">
-        <v>7.175738239999999</v>
+        <v>7.13140608</v>
       </c>
       <c r="Q63">
-        <v>7.575738239999998</v>
+        <v>7.531406079999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1345637082498075</v>
+        <v>0.1366920791465779</v>
       </c>
       <c r="T63">
-        <v>1.730169889592032</v>
+        <v>1.771655799904753</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.653492478479598</v>
+        <v>3.594565180439604</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08234779007569959</v>
+        <v>0.08230133393397425</v>
       </c>
       <c r="C64">
-        <v>36.10494761963911</v>
+        <v>35.25247480475293</v>
       </c>
       <c r="D64">
-        <v>90.26294761963911</v>
+        <v>90.31447480475293</v>
       </c>
       <c r="E64">
-        <v>13.548</v>
+        <v>14.45200000000001</v>
       </c>
       <c r="F64">
-        <v>56.048</v>
+        <v>56.95200000000001</v>
       </c>
       <c r="G64">
         <v>1.89</v>
@@ -6654,28 +6654,28 @@
         <v>12.35</v>
       </c>
       <c r="M64">
-        <v>3.4357424</v>
+        <v>3.4911576</v>
       </c>
       <c r="N64">
-        <v>8.914257599999999</v>
+        <v>8.8588424</v>
       </c>
       <c r="O64">
-        <v>1.78285152</v>
+        <v>1.77176848</v>
       </c>
       <c r="P64">
-        <v>7.13140608</v>
+        <v>7.08707392</v>
       </c>
       <c r="Q64">
-        <v>7.531406079999998</v>
+        <v>7.487073919999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1366920791465779</v>
+        <v>0.1389354971188493</v>
       </c>
       <c r="T64">
-        <v>1.771655799904753</v>
+        <v>1.815384191856</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.594565180439604</v>
+        <v>3.537508590273896</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08230133393397425</v>
+        <v>0.08368847779224892</v>
       </c>
       <c r="C65">
-        <v>35.25247480475293</v>
+        <v>32.83483574999233</v>
       </c>
       <c r="D65">
-        <v>90.31447480475293</v>
+        <v>88.80083574999233</v>
       </c>
       <c r="E65">
-        <v>14.45200000000001</v>
+        <v>15.356</v>
       </c>
       <c r="F65">
-        <v>56.95200000000001</v>
+        <v>57.856</v>
       </c>
       <c r="G65">
         <v>1.89</v>
@@ -6736,45 +6736,45 @@
         <v>12.35</v>
       </c>
       <c r="M65">
-        <v>3.4911576</v>
+        <v>3.7085696</v>
       </c>
       <c r="N65">
-        <v>8.8588424</v>
+        <v>8.641430399999999</v>
       </c>
       <c r="O65">
-        <v>1.77176848</v>
+        <v>1.72828608</v>
       </c>
       <c r="P65">
-        <v>7.08707392</v>
+        <v>6.913144319999999</v>
       </c>
       <c r="Q65">
-        <v>7.487073919999998</v>
+        <v>7.313144319999997</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1389354971188493</v>
+        <v>0.1413035494229136</v>
       </c>
       <c r="T65">
-        <v>1.815384191856</v>
+        <v>1.861541938915649</v>
       </c>
       <c r="U65">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V65">
         <v>0.2</v>
       </c>
       <c r="W65">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.537508590273896</v>
+        <v>3.330124908536164</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08368847779224892</v>
+        <v>0.08366442165052357</v>
       </c>
       <c r="C66">
-        <v>32.83483574999233</v>
+        <v>31.95665316365725</v>
       </c>
       <c r="D66">
-        <v>88.80083574999233</v>
+        <v>88.82665316365726</v>
       </c>
       <c r="E66">
-        <v>15.356</v>
+        <v>16.26000000000001</v>
       </c>
       <c r="F66">
-        <v>57.856</v>
+        <v>58.76000000000001</v>
       </c>
       <c r="G66">
         <v>1.89</v>
@@ -6818,28 +6818,28 @@
         <v>12.35</v>
       </c>
       <c r="M66">
-        <v>3.7085696</v>
+        <v>3.766516000000001</v>
       </c>
       <c r="N66">
-        <v>8.641430399999999</v>
+        <v>8.583483999999999</v>
       </c>
       <c r="O66">
-        <v>1.72828608</v>
+        <v>1.7166968</v>
       </c>
       <c r="P66">
-        <v>6.913144319999999</v>
+        <v>6.866787199999999</v>
       </c>
       <c r="Q66">
-        <v>7.313144319999997</v>
+        <v>7.266787199999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1413035494229136</v>
+        <v>0.1438069190014959</v>
       </c>
       <c r="T66">
-        <v>1.861541938915649</v>
+        <v>1.910337271521563</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.330124908536164</v>
+        <v>3.278892217635607</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08366442165052357</v>
+        <v>0.08364036550879823</v>
       </c>
       <c r="C67">
-        <v>31.95665316365725</v>
+        <v>31.07848559368286</v>
       </c>
       <c r="D67">
-        <v>88.82665316365726</v>
+        <v>88.85248559368287</v>
       </c>
       <c r="E67">
-        <v>16.26000000000001</v>
+        <v>17.16400000000001</v>
       </c>
       <c r="F67">
-        <v>58.76000000000001</v>
+        <v>59.66400000000001</v>
       </c>
       <c r="G67">
         <v>1.89</v>
@@ -6900,28 +6900,28 @@
         <v>12.35</v>
       </c>
       <c r="M67">
-        <v>3.766516000000001</v>
+        <v>3.824462400000001</v>
       </c>
       <c r="N67">
-        <v>8.583483999999999</v>
+        <v>8.5255376</v>
       </c>
       <c r="O67">
-        <v>1.7166968</v>
+        <v>1.70510752</v>
       </c>
       <c r="P67">
-        <v>6.866787199999999</v>
+        <v>6.82043008</v>
       </c>
       <c r="Q67">
-        <v>7.266787199999998</v>
+        <v>7.220430079999998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1438069190014959</v>
+        <v>0.1464575456141124</v>
       </c>
       <c r="T67">
-        <v>1.910337271521563</v>
+        <v>1.962002917810179</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.278892217635607</v>
+        <v>3.229212032519917</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08364036550879823</v>
+        <v>0.0836163093670729</v>
       </c>
       <c r="C68">
-        <v>31.07848559368286</v>
+        <v>30.20033305317413</v>
       </c>
       <c r="D68">
-        <v>88.85248559368287</v>
+        <v>88.87833305317413</v>
       </c>
       <c r="E68">
-        <v>17.16400000000001</v>
+        <v>18.068</v>
       </c>
       <c r="F68">
-        <v>59.66400000000001</v>
+        <v>60.568</v>
       </c>
       <c r="G68">
         <v>1.89</v>
@@ -6982,28 +6982,28 @@
         <v>12.35</v>
       </c>
       <c r="M68">
-        <v>3.824462400000001</v>
+        <v>3.882408800000001</v>
       </c>
       <c r="N68">
-        <v>8.5255376</v>
+        <v>8.467591199999999</v>
       </c>
       <c r="O68">
-        <v>1.70510752</v>
+        <v>1.69351824</v>
       </c>
       <c r="P68">
-        <v>6.82043008</v>
+        <v>6.77407296</v>
       </c>
       <c r="Q68">
-        <v>7.220430079999998</v>
+        <v>7.174072959999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1464575456141124</v>
+        <v>0.1492688162638573</v>
       </c>
       <c r="T68">
-        <v>1.962002917810179</v>
+        <v>2.016799815389014</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.229212032519917</v>
+        <v>3.181014838004694</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0836163093670729</v>
+        <v>0.08359225322534755</v>
       </c>
       <c r="C69">
-        <v>30.20033305317413</v>
+        <v>29.32219555525114</v>
       </c>
       <c r="D69">
-        <v>88.87833305317413</v>
+        <v>88.90419555525115</v>
       </c>
       <c r="E69">
-        <v>18.068</v>
+        <v>18.97200000000001</v>
       </c>
       <c r="F69">
-        <v>60.568</v>
+        <v>61.47200000000001</v>
       </c>
       <c r="G69">
         <v>1.89</v>
@@ -7064,28 +7064,28 @@
         <v>12.35</v>
       </c>
       <c r="M69">
-        <v>3.882408800000001</v>
+        <v>3.940355200000001</v>
       </c>
       <c r="N69">
-        <v>8.467591199999999</v>
+        <v>8.409644799999999</v>
       </c>
       <c r="O69">
-        <v>1.69351824</v>
+        <v>1.68192896</v>
       </c>
       <c r="P69">
-        <v>6.77407296</v>
+        <v>6.727715839999999</v>
       </c>
       <c r="Q69">
-        <v>7.174072959999998</v>
+        <v>7.127715839999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1492688162638573</v>
+        <v>0.1522557913292111</v>
       </c>
       <c r="T69">
-        <v>2.016799815389014</v>
+        <v>2.075021519066526</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.181014838004694</v>
+        <v>3.134235208034037</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08359225322534755</v>
+        <v>0.0835681970836222</v>
       </c>
       <c r="C70">
-        <v>29.32219555525114</v>
+        <v>28.44407311304941</v>
       </c>
       <c r="D70">
-        <v>88.90419555525115</v>
+        <v>88.93007311304942</v>
       </c>
       <c r="E70">
-        <v>18.97200000000001</v>
+        <v>19.87600000000001</v>
       </c>
       <c r="F70">
-        <v>61.47200000000001</v>
+        <v>62.37600000000001</v>
       </c>
       <c r="G70">
         <v>1.89</v>
@@ -7146,28 +7146,28 @@
         <v>12.35</v>
       </c>
       <c r="M70">
-        <v>3.940355200000001</v>
+        <v>3.998301600000001</v>
       </c>
       <c r="N70">
-        <v>8.409644799999999</v>
+        <v>8.351698399999998</v>
       </c>
       <c r="O70">
-        <v>1.68192896</v>
+        <v>1.67033968</v>
       </c>
       <c r="P70">
-        <v>6.727715839999999</v>
+        <v>6.681358719999999</v>
       </c>
       <c r="Q70">
-        <v>7.127715839999998</v>
+        <v>7.081358719999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1522557913292111</v>
+        <v>0.1554354744632974</v>
       </c>
       <c r="T70">
-        <v>2.075021519066526</v>
+        <v>2.136999461690974</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.134235208034037</v>
+        <v>3.088811509366876</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0835681970836222</v>
+        <v>0.08354414094189686</v>
       </c>
       <c r="C71">
-        <v>28.44407311304941</v>
+        <v>27.56596573971967</v>
       </c>
       <c r="D71">
-        <v>88.93007311304942</v>
+        <v>88.95596573971967</v>
       </c>
       <c r="E71">
-        <v>19.87600000000001</v>
+        <v>20.78000000000001</v>
       </c>
       <c r="F71">
-        <v>62.37600000000001</v>
+        <v>63.28000000000001</v>
       </c>
       <c r="G71">
         <v>1.89</v>
@@ -7228,28 +7228,28 @@
         <v>12.35</v>
       </c>
       <c r="M71">
-        <v>3.998301600000001</v>
+        <v>4.056248000000001</v>
       </c>
       <c r="N71">
-        <v>8.351698399999998</v>
+        <v>8.293751999999998</v>
       </c>
       <c r="O71">
-        <v>1.67033968</v>
+        <v>1.6587504</v>
       </c>
       <c r="P71">
-        <v>6.681358719999999</v>
+        <v>6.635001599999998</v>
       </c>
       <c r="Q71">
-        <v>7.081358719999997</v>
+        <v>7.035001599999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1554354744632974</v>
+        <v>0.1588271364729896</v>
       </c>
       <c r="T71">
-        <v>2.136999461690974</v>
+        <v>2.203109267157052</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.088811509366876</v>
+        <v>3.044685630661635</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08354414094189686</v>
+        <v>0.08352008480017153</v>
       </c>
       <c r="C72">
-        <v>27.56596573971967</v>
+        <v>26.68787344842792</v>
       </c>
       <c r="D72">
-        <v>88.95596573971967</v>
+        <v>88.98187344842793</v>
       </c>
       <c r="E72">
-        <v>20.78000000000001</v>
+        <v>21.68400000000001</v>
       </c>
       <c r="F72">
-        <v>63.28000000000001</v>
+        <v>64.18400000000001</v>
       </c>
       <c r="G72">
         <v>1.89</v>
@@ -7310,28 +7310,28 @@
         <v>12.35</v>
       </c>
       <c r="M72">
-        <v>4.056248000000001</v>
+        <v>4.114194400000001</v>
       </c>
       <c r="N72">
-        <v>8.293751999999998</v>
+        <v>8.235805599999999</v>
       </c>
       <c r="O72">
-        <v>1.6587504</v>
+        <v>1.64716112</v>
       </c>
       <c r="P72">
-        <v>6.635001599999998</v>
+        <v>6.588644479999999</v>
       </c>
       <c r="Q72">
-        <v>7.035001599999997</v>
+        <v>6.988644479999998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1588271364729896</v>
+        <v>0.1624527062074881</v>
       </c>
       <c r="T72">
-        <v>2.203109267157052</v>
+        <v>2.273778369551826</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.044685630661635</v>
+        <v>3.001802734455134</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08352008480017153</v>
+        <v>0.08798882865844619</v>
       </c>
       <c r="C73">
-        <v>26.68787344842794</v>
+        <v>21.21685970918273</v>
       </c>
       <c r="D73">
-        <v>88.98187344842793</v>
+        <v>84.41485970918274</v>
       </c>
       <c r="E73">
-        <v>21.684</v>
+        <v>22.58800000000001</v>
       </c>
       <c r="F73">
-        <v>64.184</v>
+        <v>65.08800000000001</v>
       </c>
       <c r="G73">
         <v>1.89</v>
@@ -7392,45 +7392,45 @@
         <v>12.35</v>
       </c>
       <c r="M73">
-        <v>4.1141944</v>
+        <v>4.679827200000001</v>
       </c>
       <c r="N73">
-        <v>8.235805599999999</v>
+        <v>7.670172799999999</v>
       </c>
       <c r="O73">
-        <v>1.64716112</v>
+        <v>1.53403456</v>
       </c>
       <c r="P73">
-        <v>6.588644479999999</v>
+        <v>6.136138239999999</v>
       </c>
       <c r="Q73">
-        <v>6.988644479999998</v>
+        <v>6.536138239999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.162452706207488</v>
+        <v>0.1663372452087364</v>
       </c>
       <c r="T73">
-        <v>2.273778369551825</v>
+        <v>2.349495264974796</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.001802734455134</v>
+        <v>2.63898632838409</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08798882865844619</v>
+        <v>0.08802717251672083</v>
       </c>
       <c r="C74">
-        <v>21.21685970918273</v>
+        <v>20.27570029951681</v>
       </c>
       <c r="D74">
-        <v>84.41485970918274</v>
+        <v>84.37770029951682</v>
       </c>
       <c r="E74">
-        <v>22.58800000000001</v>
+        <v>23.492</v>
       </c>
       <c r="F74">
-        <v>65.08800000000001</v>
+        <v>65.992</v>
       </c>
       <c r="G74">
         <v>1.89</v>
@@ -7474,28 +7474,28 @@
         <v>12.35</v>
       </c>
       <c r="M74">
-        <v>4.679827200000001</v>
+        <v>4.744824800000001</v>
       </c>
       <c r="N74">
-        <v>7.670172799999999</v>
+        <v>7.605175199999999</v>
       </c>
       <c r="O74">
-        <v>1.53403456</v>
+        <v>1.52103504</v>
       </c>
       <c r="P74">
-        <v>6.136138239999999</v>
+        <v>6.084140159999999</v>
       </c>
       <c r="Q74">
-        <v>6.536138239999998</v>
+        <v>6.484140159999997</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1663372452087364</v>
+        <v>0.1705095278397068</v>
       </c>
       <c r="T74">
-        <v>2.349495264974796</v>
+        <v>2.430820819317987</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.63898632838409</v>
+        <v>2.602835830734993</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08802717251672083</v>
+        <v>0.0880655163749955</v>
       </c>
       <c r="C75">
-        <v>20.27570029951681</v>
+        <v>19.3345735905901</v>
       </c>
       <c r="D75">
-        <v>84.37770029951682</v>
+        <v>84.3405735905901</v>
       </c>
       <c r="E75">
-        <v>23.492</v>
+        <v>24.396</v>
       </c>
       <c r="F75">
-        <v>65.992</v>
+        <v>66.896</v>
       </c>
       <c r="G75">
         <v>1.89</v>
@@ -7556,28 +7556,28 @@
         <v>12.35</v>
       </c>
       <c r="M75">
-        <v>4.744824800000001</v>
+        <v>4.809822400000001</v>
       </c>
       <c r="N75">
-        <v>7.605175199999999</v>
+        <v>7.540177599999999</v>
       </c>
       <c r="O75">
-        <v>1.52103504</v>
+        <v>1.50803552</v>
       </c>
       <c r="P75">
-        <v>6.084140159999999</v>
+        <v>6.032142079999999</v>
       </c>
       <c r="Q75">
-        <v>6.484140159999997</v>
+        <v>6.432142079999998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1705095278397068</v>
+        <v>0.1750027552884442</v>
       </c>
       <c r="T75">
-        <v>2.430820819317987</v>
+        <v>2.518402185533732</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.602835830734993</v>
+        <v>2.567662373562899</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0880655163749955</v>
+        <v>0.08810386023327016</v>
       </c>
       <c r="C76">
-        <v>19.3345735905901</v>
+        <v>18.39347953925599</v>
       </c>
       <c r="D76">
-        <v>84.3405735905901</v>
+        <v>84.303479539256</v>
       </c>
       <c r="E76">
-        <v>24.396</v>
+        <v>25.30000000000001</v>
       </c>
       <c r="F76">
-        <v>66.896</v>
+        <v>67.80000000000001</v>
       </c>
       <c r="G76">
         <v>1.89</v>
@@ -7638,28 +7638,28 @@
         <v>12.35</v>
       </c>
       <c r="M76">
-        <v>4.809822400000001</v>
+        <v>4.874820000000001</v>
       </c>
       <c r="N76">
-        <v>7.540177599999999</v>
+        <v>7.475179999999998</v>
       </c>
       <c r="O76">
-        <v>1.50803552</v>
+        <v>1.495036</v>
       </c>
       <c r="P76">
-        <v>6.032142079999999</v>
+        <v>5.980143999999998</v>
       </c>
       <c r="Q76">
-        <v>6.432142079999998</v>
+        <v>6.380143999999997</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1750027552884442</v>
+        <v>0.1798554409330806</v>
       </c>
       <c r="T76">
-        <v>2.518402185533732</v>
+        <v>2.612990061046736</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.567662373562899</v>
+        <v>2.533426875248726</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08810386023327016</v>
+        <v>0.08814220409154483</v>
       </c>
       <c r="C77">
-        <v>18.39347953925599</v>
+        <v>17.45241810244379</v>
       </c>
       <c r="D77">
-        <v>84.303479539256</v>
+        <v>84.26641810244379</v>
       </c>
       <c r="E77">
-        <v>25.30000000000001</v>
+        <v>26.20400000000001</v>
       </c>
       <c r="F77">
-        <v>67.80000000000001</v>
+        <v>68.70400000000001</v>
       </c>
       <c r="G77">
         <v>1.89</v>
@@ -7720,28 +7720,28 @@
         <v>12.35</v>
       </c>
       <c r="M77">
-        <v>4.874820000000001</v>
+        <v>4.939817600000001</v>
       </c>
       <c r="N77">
-        <v>7.475179999999998</v>
+        <v>7.410182399999998</v>
       </c>
       <c r="O77">
-        <v>1.495036</v>
+        <v>1.48203648</v>
       </c>
       <c r="P77">
-        <v>5.980143999999998</v>
+        <v>5.928145919999999</v>
       </c>
       <c r="Q77">
-        <v>6.380143999999997</v>
+        <v>6.328145919999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1798554409330806</v>
+        <v>0.1851125170481034</v>
       </c>
       <c r="T77">
-        <v>2.612990061046736</v>
+        <v>2.715460259519157</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.533426875248726</v>
+        <v>2.500092311100717</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08814220409154483</v>
+        <v>0.09058294794981948</v>
       </c>
       <c r="C78">
-        <v>17.45241810244379</v>
+        <v>14.25453381744722</v>
       </c>
       <c r="D78">
-        <v>84.26641810244379</v>
+        <v>81.97253381744723</v>
       </c>
       <c r="E78">
-        <v>26.20400000000001</v>
+        <v>27.108</v>
       </c>
       <c r="F78">
-        <v>68.70400000000001</v>
+        <v>69.608</v>
       </c>
       <c r="G78">
         <v>1.89</v>
@@ -7802,45 +7802,45 @@
         <v>12.35</v>
       </c>
       <c r="M78">
-        <v>4.939817600000001</v>
+        <v>5.276286400000001</v>
       </c>
       <c r="N78">
-        <v>7.410182399999998</v>
+        <v>7.073713599999999</v>
       </c>
       <c r="O78">
-        <v>1.48203648</v>
+        <v>1.41474272</v>
       </c>
       <c r="P78">
-        <v>5.928145919999999</v>
+        <v>5.658970879999999</v>
       </c>
       <c r="Q78">
-        <v>6.328145919999997</v>
+        <v>6.058970879999998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1851125170481034</v>
+        <v>0.1908267302166064</v>
       </c>
       <c r="T78">
-        <v>2.715460259519157</v>
+        <v>2.826840910032658</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.2</v>
       </c>
       <c r="W78">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.500092311100717</v>
+        <v>2.340661416711572</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09058294794981948</v>
+        <v>0.09065249180809413</v>
       </c>
       <c r="C79">
-        <v>14.25453381744722</v>
+        <v>13.28700289110219</v>
       </c>
       <c r="D79">
-        <v>81.97253381744723</v>
+        <v>81.90900289110219</v>
       </c>
       <c r="E79">
-        <v>27.108</v>
+        <v>28.012</v>
       </c>
       <c r="F79">
-        <v>69.608</v>
+        <v>70.512</v>
       </c>
       <c r="G79">
         <v>1.89</v>
@@ -7884,28 +7884,28 @@
         <v>12.35</v>
       </c>
       <c r="M79">
-        <v>5.276286400000001</v>
+        <v>5.3448096</v>
       </c>
       <c r="N79">
-        <v>7.073713599999999</v>
+        <v>7.005190399999999</v>
       </c>
       <c r="O79">
-        <v>1.41474272</v>
+        <v>1.40103808</v>
       </c>
       <c r="P79">
-        <v>5.658970879999999</v>
+        <v>5.604152319999999</v>
       </c>
       <c r="Q79">
-        <v>6.058970879999998</v>
+        <v>6.004152319999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1908267302166064</v>
+        <v>0.1970604173095188</v>
       </c>
       <c r="T79">
-        <v>2.826840910032658</v>
+        <v>2.948347074229205</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.340661416711572</v>
+        <v>2.310652937010142</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09065249180809413</v>
+        <v>0.0907220356663688</v>
       </c>
       <c r="C80">
-        <v>13.28700289110219</v>
+        <v>12.31957036485996</v>
       </c>
       <c r="D80">
-        <v>81.90900289110219</v>
+        <v>81.84557036485997</v>
       </c>
       <c r="E80">
-        <v>28.012</v>
+        <v>28.91600000000001</v>
       </c>
       <c r="F80">
-        <v>70.512</v>
+        <v>71.41600000000001</v>
       </c>
       <c r="G80">
         <v>1.89</v>
@@ -7966,28 +7966,28 @@
         <v>12.35</v>
       </c>
       <c r="M80">
-        <v>5.3448096</v>
+        <v>5.413332800000001</v>
       </c>
       <c r="N80">
-        <v>7.005190399999999</v>
+        <v>6.936667199999999</v>
       </c>
       <c r="O80">
-        <v>1.40103808</v>
+        <v>1.38733344</v>
       </c>
       <c r="P80">
-        <v>5.604152319999999</v>
+        <v>5.549333759999999</v>
       </c>
       <c r="Q80">
-        <v>6.004152319999998</v>
+        <v>5.949333759999997</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1970604173095188</v>
+        <v>0.2038877888874705</v>
       </c>
       <c r="T80">
-        <v>2.948347074229205</v>
+        <v>3.081425254063519</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.310652937010142</v>
+        <v>2.281404165655582</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0907220356663688</v>
+        <v>0.09079157952464345</v>
       </c>
       <c r="C81">
-        <v>12.31957036485996</v>
+        <v>11.35223601028642</v>
       </c>
       <c r="D81">
-        <v>81.84557036485997</v>
+        <v>81.78223601028643</v>
       </c>
       <c r="E81">
-        <v>28.91600000000001</v>
+        <v>29.82000000000001</v>
       </c>
       <c r="F81">
-        <v>71.41600000000001</v>
+        <v>72.32000000000001</v>
       </c>
       <c r="G81">
         <v>1.89</v>
@@ -8048,28 +8048,28 @@
         <v>12.35</v>
       </c>
       <c r="M81">
-        <v>5.413332800000001</v>
+        <v>5.481856000000001</v>
       </c>
       <c r="N81">
-        <v>6.936667199999999</v>
+        <v>6.868143999999998</v>
       </c>
       <c r="O81">
-        <v>1.38733344</v>
+        <v>1.3736288</v>
       </c>
       <c r="P81">
-        <v>5.549333759999999</v>
+        <v>5.494515199999999</v>
       </c>
       <c r="Q81">
-        <v>5.949333759999997</v>
+        <v>5.894515199999997</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2038877888874705</v>
+        <v>0.2113978976232173</v>
       </c>
       <c r="T81">
-        <v>3.081425254063519</v>
+        <v>3.227811251881263</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.281404165655582</v>
+        <v>2.252886613584888</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09079157952464345</v>
+        <v>0.09086112338291812</v>
       </c>
       <c r="C82">
-        <v>11.35223601028642</v>
+        <v>10.38499959965395</v>
       </c>
       <c r="D82">
-        <v>81.78223601028643</v>
+        <v>81.71899959965396</v>
       </c>
       <c r="E82">
-        <v>29.82000000000001</v>
+        <v>30.724</v>
       </c>
       <c r="F82">
-        <v>72.32000000000001</v>
+        <v>73.224</v>
       </c>
       <c r="G82">
         <v>1.89</v>
@@ -8130,28 +8130,28 @@
         <v>12.35</v>
       </c>
       <c r="M82">
-        <v>5.481856000000001</v>
+        <v>5.550379200000001</v>
       </c>
       <c r="N82">
-        <v>6.868143999999998</v>
+        <v>6.799620799999999</v>
       </c>
       <c r="O82">
-        <v>1.3736288</v>
+        <v>1.35992416</v>
       </c>
       <c r="P82">
-        <v>5.494515199999999</v>
+        <v>5.439696639999999</v>
       </c>
       <c r="Q82">
-        <v>5.894515199999997</v>
+        <v>5.839696639999998</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2113978976232173</v>
+        <v>0.2196985441206217</v>
       </c>
       <c r="T82">
-        <v>3.227811251881263</v>
+        <v>3.389606302100876</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.252886613584888</v>
+        <v>2.225073198602358</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09086112338291812</v>
+        <v>0.09093066724119277</v>
       </c>
       <c r="C83">
-        <v>10.38499959965395</v>
+        <v>9.417860905938781</v>
       </c>
       <c r="D83">
-        <v>81.71899959965396</v>
+        <v>81.65586090593879</v>
       </c>
       <c r="E83">
-        <v>30.724</v>
+        <v>31.62800000000001</v>
       </c>
       <c r="F83">
-        <v>73.224</v>
+        <v>74.12800000000001</v>
       </c>
       <c r="G83">
         <v>1.89</v>
@@ -8212,28 +8212,28 @@
         <v>12.35</v>
       </c>
       <c r="M83">
-        <v>5.550379200000001</v>
+        <v>5.618902400000001</v>
       </c>
       <c r="N83">
-        <v>6.799620799999999</v>
+        <v>6.731097599999998</v>
       </c>
       <c r="O83">
-        <v>1.35992416</v>
+        <v>1.34621952</v>
       </c>
       <c r="P83">
-        <v>5.439696639999999</v>
+        <v>5.384878079999998</v>
       </c>
       <c r="Q83">
-        <v>5.839696639999998</v>
+        <v>5.784878079999997</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2196985441206217</v>
+        <v>0.2289214846732932</v>
       </c>
       <c r="T83">
-        <v>3.389606302100876</v>
+        <v>3.569378580122666</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.225073198602358</v>
+        <v>2.197938159595012</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09093066724119277</v>
+        <v>0.09100021109946743</v>
       </c>
       <c r="C84">
-        <v>9.417860905938781</v>
+        <v>8.450819702818194</v>
       </c>
       <c r="D84">
-        <v>81.65586090593879</v>
+        <v>81.5928197028182</v>
       </c>
       <c r="E84">
-        <v>31.62800000000001</v>
+        <v>32.53200000000001</v>
       </c>
       <c r="F84">
-        <v>74.12800000000001</v>
+        <v>75.03200000000001</v>
       </c>
       <c r="G84">
         <v>1.89</v>
@@ -8294,28 +8294,28 @@
         <v>12.35</v>
       </c>
       <c r="M84">
-        <v>5.618902400000001</v>
+        <v>5.687425600000001</v>
       </c>
       <c r="N84">
-        <v>6.731097599999998</v>
+        <v>6.662574399999999</v>
       </c>
       <c r="O84">
-        <v>1.34621952</v>
+        <v>1.33251488</v>
       </c>
       <c r="P84">
-        <v>5.384878079999998</v>
+        <v>5.330059519999999</v>
       </c>
       <c r="Q84">
-        <v>5.784878079999997</v>
+        <v>5.730059519999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2289214846732932</v>
+        <v>0.2392294770556908</v>
       </c>
       <c r="T84">
-        <v>3.569378580122666</v>
+        <v>3.770300537911728</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.197938159595012</v>
+        <v>2.17145697694929</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09100021109946743</v>
+        <v>0.09106975495774208</v>
       </c>
       <c r="C85">
-        <v>8.450819702818194</v>
+        <v>7.483875764667857</v>
       </c>
       <c r="D85">
-        <v>81.5928197028182</v>
+        <v>81.52987576466786</v>
       </c>
       <c r="E85">
-        <v>32.53200000000001</v>
+        <v>33.43600000000001</v>
       </c>
       <c r="F85">
-        <v>75.03200000000001</v>
+        <v>75.93600000000001</v>
       </c>
       <c r="G85">
         <v>1.89</v>
@@ -8376,28 +8376,28 @@
         <v>12.35</v>
       </c>
       <c r="M85">
-        <v>5.687425600000001</v>
+        <v>5.755948800000001</v>
       </c>
       <c r="N85">
-        <v>6.662574399999999</v>
+        <v>6.594051199999998</v>
       </c>
       <c r="O85">
-        <v>1.33251488</v>
+        <v>1.31881024</v>
       </c>
       <c r="P85">
-        <v>5.330059519999999</v>
+        <v>5.275240959999999</v>
       </c>
       <c r="Q85">
-        <v>5.730059519999998</v>
+        <v>5.675240959999997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2392294770556908</v>
+        <v>0.2508259684858881</v>
       </c>
       <c r="T85">
-        <v>3.770300537911728</v>
+        <v>3.996337740424422</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.17145697694929</v>
+        <v>2.145606298652273</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09106975495774208</v>
+        <v>0.09113929881601676</v>
       </c>
       <c r="C86">
-        <v>7.483875764667857</v>
+        <v>6.517028866559102</v>
       </c>
       <c r="D86">
-        <v>81.52987576466786</v>
+        <v>81.4670288665591</v>
       </c>
       <c r="E86">
-        <v>33.43600000000001</v>
+        <v>34.34</v>
       </c>
       <c r="F86">
-        <v>75.93600000000001</v>
+        <v>76.84</v>
       </c>
       <c r="G86">
         <v>1.89</v>
@@ -8458,28 +8458,28 @@
         <v>12.35</v>
       </c>
       <c r="M86">
-        <v>5.755948800000001</v>
+        <v>5.824472000000001</v>
       </c>
       <c r="N86">
-        <v>6.594051199999998</v>
+        <v>6.525527999999999</v>
       </c>
       <c r="O86">
-        <v>1.31881024</v>
+        <v>1.3051056</v>
       </c>
       <c r="P86">
-        <v>5.275240959999999</v>
+        <v>5.220422399999999</v>
       </c>
       <c r="Q86">
-        <v>5.675240959999997</v>
+        <v>5.620422399999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.250825968485888</v>
+        <v>0.2639686587734449</v>
       </c>
       <c r="T86">
-        <v>3.996337740424419</v>
+        <v>4.252513236605473</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.145606298652273</v>
+        <v>2.120363871609306</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09113929881601676</v>
+        <v>0.09120884267429141</v>
       </c>
       <c r="C87">
-        <v>6.517028866559102</v>
+        <v>5.550278784256307</v>
       </c>
       <c r="D87">
-        <v>81.4670288665591</v>
+        <v>81.40427878425631</v>
       </c>
       <c r="E87">
-        <v>34.34</v>
+        <v>35.244</v>
       </c>
       <c r="F87">
-        <v>76.84</v>
+        <v>77.744</v>
       </c>
       <c r="G87">
         <v>1.89</v>
@@ -8540,28 +8540,28 @@
         <v>12.35</v>
       </c>
       <c r="M87">
-        <v>5.824472000000001</v>
+        <v>5.892995200000001</v>
       </c>
       <c r="N87">
-        <v>6.525527999999999</v>
+        <v>6.457004799999999</v>
       </c>
       <c r="O87">
-        <v>1.3051056</v>
+        <v>1.29140096</v>
       </c>
       <c r="P87">
-        <v>5.220422399999999</v>
+        <v>5.165603839999999</v>
       </c>
       <c r="Q87">
-        <v>5.620422399999997</v>
+        <v>5.565603839999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2639686587734449</v>
+        <v>0.2789888762449386</v>
       </c>
       <c r="T87">
-        <v>4.252513236605473</v>
+        <v>4.545285232240961</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.120363871609306</v>
+        <v>2.095708477753384</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09120884267429141</v>
+        <v>0.09127838653256606</v>
       </c>
       <c r="C88">
-        <v>5.550278784256307</v>
+        <v>4.583625294214116</v>
       </c>
       <c r="D88">
-        <v>81.40427878425631</v>
+        <v>81.34162529421413</v>
       </c>
       <c r="E88">
-        <v>35.244</v>
+        <v>36.14800000000001</v>
       </c>
       <c r="F88">
-        <v>77.744</v>
+        <v>78.64800000000001</v>
       </c>
       <c r="G88">
         <v>1.89</v>
@@ -8622,28 +8622,28 @@
         <v>12.35</v>
       </c>
       <c r="M88">
-        <v>5.892995200000001</v>
+        <v>5.961518400000001</v>
       </c>
       <c r="N88">
-        <v>6.457004799999999</v>
+        <v>6.388481599999999</v>
       </c>
       <c r="O88">
-        <v>1.29140096</v>
+        <v>1.27769632</v>
       </c>
       <c r="P88">
-        <v>5.165603839999999</v>
+        <v>5.110785279999999</v>
       </c>
       <c r="Q88">
-        <v>5.565603839999998</v>
+        <v>5.510785279999998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2789888762449386</v>
+        <v>0.2963198964043543</v>
       </c>
       <c r="T88">
-        <v>4.545285232240961</v>
+        <v>4.883099073358832</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.095708477753384</v>
+        <v>2.071619874560816</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09127838653256606</v>
+        <v>0.09134793039084071</v>
       </c>
       <c r="C89">
-        <v>4.583625294214116</v>
+        <v>3.617068173574978</v>
       </c>
       <c r="D89">
-        <v>81.34162529421413</v>
+        <v>81.27906817357498</v>
       </c>
       <c r="E89">
-        <v>36.14800000000001</v>
+        <v>37.05200000000001</v>
       </c>
       <c r="F89">
-        <v>78.64800000000001</v>
+        <v>79.55200000000001</v>
       </c>
       <c r="G89">
         <v>1.89</v>
@@ -8704,28 +8704,28 @@
         <v>12.35</v>
       </c>
       <c r="M89">
-        <v>5.961518400000001</v>
+        <v>6.030041600000001</v>
       </c>
       <c r="N89">
-        <v>6.388481599999999</v>
+        <v>6.319958399999998</v>
       </c>
       <c r="O89">
-        <v>1.27769632</v>
+        <v>1.26399168</v>
       </c>
       <c r="P89">
-        <v>5.110785279999999</v>
+        <v>5.055966719999999</v>
       </c>
       <c r="Q89">
-        <v>5.510785279999998</v>
+        <v>5.455966719999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2963198964043543</v>
+        <v>0.3165394199236726</v>
       </c>
       <c r="T89">
-        <v>4.883099073358832</v>
+        <v>5.277215221329683</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.071619874560816</v>
+        <v>2.048078739622625</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09134793039084071</v>
+        <v>0.09141747424911538</v>
       </c>
       <c r="C90">
-        <v>3.617068173574978</v>
+        <v>2.650607200166263</v>
       </c>
       <c r="D90">
-        <v>81.27906817357498</v>
+        <v>81.21660720016627</v>
       </c>
       <c r="E90">
-        <v>37.05200000000001</v>
+        <v>37.956</v>
       </c>
       <c r="F90">
-        <v>79.55200000000001</v>
+        <v>80.456</v>
       </c>
       <c r="G90">
         <v>1.89</v>
@@ -8786,28 +8786,28 @@
         <v>12.35</v>
       </c>
       <c r="M90">
-        <v>6.030041600000001</v>
+        <v>6.098564800000001</v>
       </c>
       <c r="N90">
-        <v>6.319958399999998</v>
+        <v>6.251435199999999</v>
       </c>
       <c r="O90">
-        <v>1.26399168</v>
+        <v>1.25028704</v>
       </c>
       <c r="P90">
-        <v>5.055966719999999</v>
+        <v>5.001148159999999</v>
       </c>
       <c r="Q90">
-        <v>5.455966719999997</v>
+        <v>5.401148159999997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3165394199236726</v>
+        <v>0.3404352204465034</v>
       </c>
       <c r="T90">
-        <v>5.277215221329683</v>
+        <v>5.742988850749779</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.048078739622625</v>
+        <v>2.025066618952708</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09141747424911538</v>
+        <v>0.09148701810739004</v>
       </c>
       <c r="C91">
-        <v>2.650607200166263</v>
+        <v>1.684242152497802</v>
       </c>
       <c r="D91">
-        <v>81.21660720016627</v>
+        <v>81.15424215249782</v>
       </c>
       <c r="E91">
-        <v>37.956</v>
+        <v>38.86000000000001</v>
       </c>
       <c r="F91">
-        <v>80.456</v>
+        <v>81.36000000000001</v>
       </c>
       <c r="G91">
         <v>1.89</v>
@@ -8868,28 +8868,28 @@
         <v>12.35</v>
       </c>
       <c r="M91">
-        <v>6.098564800000001</v>
+        <v>6.167088000000001</v>
       </c>
       <c r="N91">
-        <v>6.251435199999999</v>
+        <v>6.182911999999998</v>
       </c>
       <c r="O91">
-        <v>1.25028704</v>
+        <v>1.2365824</v>
       </c>
       <c r="P91">
-        <v>5.001148159999999</v>
+        <v>4.946329599999999</v>
       </c>
       <c r="Q91">
-        <v>5.401148159999997</v>
+        <v>5.346329599999997</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3404352204465034</v>
+        <v>0.3691101810739004</v>
       </c>
       <c r="T91">
-        <v>5.742988850749779</v>
+        <v>6.301917206053894</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.025066618952708</v>
+        <v>2.002565878742122</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09148701810739004</v>
+        <v>0.1018941619656647</v>
       </c>
       <c r="C92">
-        <v>1.684242152497802</v>
+        <v>-7.584247264774405</v>
       </c>
       <c r="D92">
-        <v>81.15424215249782</v>
+        <v>72.7897527352256</v>
       </c>
       <c r="E92">
-        <v>38.86000000000001</v>
+        <v>39.76400000000001</v>
       </c>
       <c r="F92">
-        <v>81.36000000000001</v>
+        <v>82.26400000000001</v>
       </c>
       <c r="G92">
         <v>1.89</v>
@@ -8950,45 +8950,45 @@
         <v>12.35</v>
       </c>
       <c r="M92">
-        <v>6.167088000000001</v>
+        <v>7.403760000000001</v>
       </c>
       <c r="N92">
-        <v>6.182911999999998</v>
+        <v>4.946239999999999</v>
       </c>
       <c r="O92">
-        <v>1.2365824</v>
+        <v>0.9892479999999998</v>
       </c>
       <c r="P92">
-        <v>4.946329599999999</v>
+        <v>3.956991999999999</v>
       </c>
       <c r="Q92">
-        <v>5.346329599999997</v>
+        <v>4.356991999999997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3691101810739004</v>
+        <v>0.4041573551740523</v>
       </c>
       <c r="T92">
-        <v>6.301917206053894</v>
+        <v>6.985051862536702</v>
       </c>
       <c r="U92">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V92">
         <v>0.2</v>
       </c>
       <c r="W92">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.002565878742122</v>
+        <v>1.668071358336845</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1018941619656647</v>
+        <v>0.1020773058239393</v>
       </c>
       <c r="C93">
-        <v>-7.584247264774405</v>
+        <v>-8.62003416585425</v>
       </c>
       <c r="D93">
-        <v>72.7897527352256</v>
+        <v>72.65796583414576</v>
       </c>
       <c r="E93">
-        <v>39.76400000000001</v>
+        <v>40.66800000000001</v>
       </c>
       <c r="F93">
-        <v>82.26400000000001</v>
+        <v>83.16800000000001</v>
       </c>
       <c r="G93">
         <v>1.89</v>
@@ -9032,28 +9032,28 @@
         <v>12.35</v>
       </c>
       <c r="M93">
-        <v>7.403760000000001</v>
+        <v>7.48512</v>
       </c>
       <c r="N93">
-        <v>4.946239999999999</v>
+        <v>4.864879999999999</v>
       </c>
       <c r="O93">
-        <v>0.9892479999999998</v>
+        <v>0.972976</v>
       </c>
       <c r="P93">
-        <v>3.956991999999999</v>
+        <v>3.891903999999999</v>
       </c>
       <c r="Q93">
-        <v>4.356991999999997</v>
+        <v>4.291903999999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4041573551740523</v>
+        <v>0.4479663227992421</v>
       </c>
       <c r="T93">
-        <v>6.985051862536702</v>
+        <v>7.838970183140213</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.668071358336845</v>
+        <v>1.64994014792014</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1020773058239393</v>
+        <v>0.102260449682214</v>
       </c>
       <c r="C94">
-        <v>-8.62003416585425</v>
+        <v>-9.655344725173279</v>
       </c>
       <c r="D94">
-        <v>72.65796583414576</v>
+        <v>72.52665527482672</v>
       </c>
       <c r="E94">
-        <v>40.66800000000001</v>
+        <v>41.572</v>
       </c>
       <c r="F94">
-        <v>83.16800000000001</v>
+        <v>84.072</v>
       </c>
       <c r="G94">
         <v>1.89</v>
@@ -9114,28 +9114,28 @@
         <v>12.35</v>
       </c>
       <c r="M94">
-        <v>7.48512</v>
+        <v>7.56648</v>
       </c>
       <c r="N94">
-        <v>4.864879999999999</v>
+        <v>4.783519999999999</v>
       </c>
       <c r="O94">
-        <v>0.972976</v>
+        <v>0.9567039999999999</v>
       </c>
       <c r="P94">
-        <v>3.891903999999999</v>
+        <v>3.826816</v>
       </c>
       <c r="Q94">
-        <v>4.291903999999998</v>
+        <v>4.226815999999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4479663227992421</v>
+        <v>0.5042921383173433</v>
       </c>
       <c r="T94">
-        <v>7.838970183140213</v>
+        <v>8.936865166773297</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.64994014792014</v>
+        <v>1.63219885600702</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.102260449682214</v>
+        <v>0.1024435935404887</v>
       </c>
       <c r="C95">
-        <v>-9.655344725173279</v>
+        <v>-10.69018152066765</v>
       </c>
       <c r="D95">
-        <v>72.52665527482672</v>
+        <v>72.39581847933236</v>
       </c>
       <c r="E95">
-        <v>41.572</v>
+        <v>42.47600000000001</v>
       </c>
       <c r="F95">
-        <v>84.072</v>
+        <v>84.97600000000001</v>
       </c>
       <c r="G95">
         <v>1.89</v>
@@ -9196,28 +9196,28 @@
         <v>12.35</v>
       </c>
       <c r="M95">
-        <v>7.56648</v>
+        <v>7.647840000000001</v>
       </c>
       <c r="N95">
-        <v>4.783519999999999</v>
+        <v>4.702159999999998</v>
       </c>
       <c r="O95">
-        <v>0.9567039999999999</v>
+        <v>0.9404319999999997</v>
       </c>
       <c r="P95">
-        <v>3.826816</v>
+        <v>3.761727999999999</v>
       </c>
       <c r="Q95">
-        <v>4.226815999999998</v>
+        <v>4.161727999999997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5042921383173433</v>
+        <v>0.5793932256748116</v>
       </c>
       <c r="T95">
-        <v>8.936865166773297</v>
+        <v>10.40072514495074</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.63219885600702</v>
+        <v>1.614835038389924</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1024435935404887</v>
+        <v>0.1026267373987633</v>
       </c>
       <c r="C96">
-        <v>-10.69018152066765</v>
+        <v>-11.72454711170487</v>
       </c>
       <c r="D96">
-        <v>72.39581847933236</v>
+        <v>72.26545288829514</v>
       </c>
       <c r="E96">
-        <v>42.47600000000001</v>
+        <v>43.38000000000001</v>
       </c>
       <c r="F96">
-        <v>84.97600000000001</v>
+        <v>85.88000000000001</v>
       </c>
       <c r="G96">
         <v>1.89</v>
@@ -9278,28 +9278,28 @@
         <v>12.35</v>
       </c>
       <c r="M96">
-        <v>7.647840000000001</v>
+        <v>7.729200000000001</v>
       </c>
       <c r="N96">
-        <v>4.702159999999998</v>
+        <v>4.620799999999999</v>
       </c>
       <c r="O96">
-        <v>0.9404319999999997</v>
+        <v>0.9241599999999999</v>
       </c>
       <c r="P96">
-        <v>3.761727999999999</v>
+        <v>3.696639999999999</v>
       </c>
       <c r="Q96">
-        <v>4.161727999999997</v>
+        <v>4.096639999999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5793932256748116</v>
+        <v>0.6845347479752674</v>
       </c>
       <c r="T96">
-        <v>10.40072514495074</v>
+        <v>12.45012911439917</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9316,7 +9316,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.614835038389924</v>
+        <v>1.597836774827925</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1026267373987633</v>
+        <v>0.102809881257038</v>
       </c>
       <c r="C97">
-        <v>-11.72454711170487</v>
+        <v>-12.75844403925053</v>
       </c>
       <c r="D97">
-        <v>72.26545288829514</v>
+        <v>72.13555596074947</v>
       </c>
       <c r="E97">
-        <v>43.38000000000001</v>
+        <v>44.28400000000001</v>
       </c>
       <c r="F97">
-        <v>85.88000000000001</v>
+        <v>86.78400000000001</v>
       </c>
       <c r="G97">
         <v>1.89</v>
@@ -9360,28 +9360,28 @@
         <v>12.35</v>
       </c>
       <c r="M97">
-        <v>7.729200000000001</v>
+        <v>7.810560000000001</v>
       </c>
       <c r="N97">
-        <v>4.620799999999999</v>
+        <v>4.539439999999999</v>
       </c>
       <c r="O97">
-        <v>0.9241599999999999</v>
+        <v>0.9078879999999998</v>
       </c>
       <c r="P97">
-        <v>3.696639999999999</v>
+        <v>3.631551999999999</v>
       </c>
       <c r="Q97">
-        <v>4.096639999999998</v>
+        <v>4.031551999999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6845347479752674</v>
+        <v>0.842247031425951</v>
       </c>
       <c r="T97">
-        <v>12.45012911439917</v>
+        <v>15.52423506857181</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.597836774827925</v>
+        <v>1.581192641756801</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.102809881257038</v>
+        <v>0.1029930251153127</v>
       </c>
       <c r="C98">
-        <v>-12.75844403925053</v>
+        <v>-13.79187482603363</v>
       </c>
       <c r="D98">
-        <v>72.13555596074947</v>
+        <v>72.00612517396637</v>
       </c>
       <c r="E98">
-        <v>44.28400000000001</v>
+        <v>45.188</v>
       </c>
       <c r="F98">
-        <v>86.78400000000001</v>
+        <v>87.688</v>
       </c>
       <c r="G98">
         <v>1.89</v>
@@ -9442,28 +9442,28 @@
         <v>12.35</v>
       </c>
       <c r="M98">
-        <v>7.810560000000001</v>
+        <v>7.89192</v>
       </c>
       <c r="N98">
-        <v>4.539439999999999</v>
+        <v>4.45808</v>
       </c>
       <c r="O98">
-        <v>0.9078879999999998</v>
+        <v>0.891616</v>
       </c>
       <c r="P98">
-        <v>3.631551999999999</v>
+        <v>3.566464</v>
       </c>
       <c r="Q98">
-        <v>4.031551999999998</v>
+        <v>3.966463999999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8422470314259489</v>
+        <v>1.105100837177087</v>
       </c>
       <c r="T98">
-        <v>15.52423506857177</v>
+        <v>20.64774499219282</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.581192641756801</v>
+        <v>1.564891686687143</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1029930251153127</v>
+        <v>0.1031761689735873</v>
       </c>
       <c r="C99">
-        <v>-13.79187482603363</v>
+        <v>-14.82484197670964</v>
       </c>
       <c r="D99">
-        <v>72.00612517396637</v>
+        <v>71.87715802329036</v>
       </c>
       <c r="E99">
-        <v>45.188</v>
+        <v>46.092</v>
       </c>
       <c r="F99">
-        <v>87.688</v>
+        <v>88.592</v>
       </c>
       <c r="G99">
         <v>1.89</v>
@@ -9524,28 +9524,28 @@
         <v>12.35</v>
       </c>
       <c r="M99">
-        <v>7.89192</v>
+        <v>7.97328</v>
       </c>
       <c r="N99">
-        <v>4.45808</v>
+        <v>4.37672</v>
       </c>
       <c r="O99">
-        <v>0.891616</v>
+        <v>0.875344</v>
       </c>
       <c r="P99">
-        <v>3.566464</v>
+        <v>3.501376</v>
       </c>
       <c r="Q99">
-        <v>3.966463999999998</v>
+        <v>3.901375999999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.105100837177087</v>
+        <v>1.630808448679364</v>
       </c>
       <c r="T99">
-        <v>20.64774499219282</v>
+        <v>30.89476483943491</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.564891686687143</v>
+        <v>1.548923404169928</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1031761689735873</v>
+        <v>0.1033593128318619</v>
       </c>
       <c r="C100">
-        <v>-14.82484197670964</v>
+        <v>-15.85734797802219</v>
       </c>
       <c r="D100">
-        <v>71.87715802329036</v>
+        <v>71.74865202197782</v>
       </c>
       <c r="E100">
-        <v>46.092</v>
+        <v>46.99600000000001</v>
       </c>
       <c r="F100">
-        <v>88.592</v>
+        <v>89.49600000000001</v>
       </c>
       <c r="G100">
         <v>1.89</v>
@@ -9606,28 +9606,28 @@
         <v>12.35</v>
       </c>
       <c r="M100">
-        <v>7.97328</v>
+        <v>8.054640000000001</v>
       </c>
       <c r="N100">
-        <v>4.37672</v>
+        <v>4.295359999999999</v>
       </c>
       <c r="O100">
-        <v>0.875344</v>
+        <v>0.8590719999999998</v>
       </c>
       <c r="P100">
-        <v>3.501376</v>
+        <v>3.436287999999999</v>
       </c>
       <c r="Q100">
-        <v>3.901375999999998</v>
+        <v>3.836287999999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.630808448679364</v>
+        <v>3.207931283186193</v>
       </c>
       <c r="T100">
-        <v>30.89476483943491</v>
+        <v>61.63582438116119</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.548923404169928</v>
+        <v>1.533277713218716</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1033593128318619</v>
-      </c>
-      <c r="C101">
-        <v>-15.85734797802219</v>
-      </c>
-      <c r="D101">
-        <v>71.74865202197782</v>
-      </c>
-      <c r="E101">
-        <v>46.99600000000001</v>
-      </c>
-      <c r="F101">
-        <v>89.49600000000001</v>
-      </c>
-      <c r="G101">
-        <v>1.89</v>
-      </c>
-      <c r="H101">
-        <v>47.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.75</v>
-      </c>
-      <c r="K101">
-        <v>0.3999999999999986</v>
-      </c>
-      <c r="L101">
-        <v>12.35</v>
-      </c>
-      <c r="M101">
-        <v>8.054640000000001</v>
-      </c>
-      <c r="N101">
-        <v>4.295359999999999</v>
-      </c>
-      <c r="O101">
-        <v>0.8590719999999998</v>
-      </c>
-      <c r="P101">
-        <v>3.436287999999999</v>
-      </c>
-      <c r="Q101">
-        <v>3.836287999999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.207931283186193</v>
-      </c>
-      <c r="T101">
-        <v>61.63582438116119</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.533277713218716</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
